--- a/src/static/xlsx/cleaned_data.xlsx
+++ b/src/static/xlsx/cleaned_data.xlsx
@@ -5404,10 +5404,10 @@
         <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>6.8</v>
+        <v>6.828</v>
       </c>
       <c r="J65" t="n">
-        <v>8453</v>
+        <v>8454</v>
       </c>
       <c r="K65" t="n">
         <v>200000000</v>
@@ -6092,7 +6092,7 @@
         <v>7.085</v>
       </c>
       <c r="J74" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="K74" t="n">
         <v>85000000</v>

--- a/src/static/xlsx/cleaned_data.xlsx
+++ b/src/static/xlsx/cleaned_data.xlsx
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5.167</v>
+        <v>26.3784</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>44909</v>
@@ -561,10 +561,10 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>7.606</v>
+        <v>7.607</v>
       </c>
       <c r="J2" t="n">
-        <v>12339</v>
+        <v>12403</v>
       </c>
       <c r="K2" t="n">
         <v>460000000</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5.295</v>
+        <v>29.0789</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>44545</v>
@@ -638,10 +638,10 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>7.948</v>
+        <v>7.947</v>
       </c>
       <c r="J3" t="n">
-        <v>20589</v>
+        <v>20634</v>
       </c>
       <c r="K3" t="n">
         <v>200000000</v>
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5.305</v>
+        <v>53.9804</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>45454</v>
@@ -715,10 +715,10 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>7.6</v>
+        <v>7.557</v>
       </c>
       <c r="J4" t="n">
-        <v>5647</v>
+        <v>5698</v>
       </c>
       <c r="K4" t="n">
         <v>200000000</v>
@@ -778,7 +778,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5.948</v>
+        <v>30.1254</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>44702</v>
@@ -792,10 +792,10 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>8.183999999999999</v>
+        <v>8.182</v>
       </c>
       <c r="J5" t="n">
-        <v>9646</v>
+        <v>9685</v>
       </c>
       <c r="K5" t="n">
         <v>170000000</v>
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5.677</v>
+        <v>22.6255</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>45126</v>
@@ -869,10 +869,10 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>6.982</v>
+        <v>6.981</v>
       </c>
       <c r="J6" t="n">
-        <v>9666</v>
+        <v>9730</v>
       </c>
       <c r="K6" t="n">
         <v>145000000</v>
@@ -932,7 +932,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4.845</v>
+        <v>26.1428</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>45021</v>
@@ -946,10 +946,10 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>7.627</v>
+        <v>7.626</v>
       </c>
       <c r="J7" t="n">
-        <v>9517</v>
+        <v>9554</v>
       </c>
       <c r="K7" t="n">
         <v>100000000</v>
@@ -962,7 +962,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Animación, Familia, Aventura, Fantasía, Comedia</t>
+          <t>Familia, Comedia, Aventura, Animación</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1009,7 +1009,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5.328</v>
+        <v>66.9084</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>45497</v>
@@ -1023,10 +1023,10 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>7.614</v>
+        <v>7.6</v>
       </c>
       <c r="J8" t="n">
-        <v>6881</v>
+        <v>6968</v>
       </c>
       <c r="K8" t="n">
         <v>200000000</v>
@@ -1086,7 +1086,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>11.844</v>
+        <v>220.0556</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>45617</v>
@@ -1100,10 +1100,10 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>7.153</v>
+        <v>7.118</v>
       </c>
       <c r="J9" t="n">
-        <v>1917</v>
+        <v>2096</v>
       </c>
       <c r="K9" t="n">
         <v>150000000</v>
@@ -1163,7 +1163,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4.097</v>
+        <v>18.5198</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>44713</v>
@@ -1177,10 +1177,10 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>6.674</v>
+        <v>6.7</v>
       </c>
       <c r="J10" t="n">
-        <v>6273</v>
+        <v>6297</v>
       </c>
       <c r="K10" t="n">
         <v>165000000</v>
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4.572</v>
+        <v>63.4427</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>45463</v>
@@ -1254,10 +1254,10 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>7.1</v>
+        <v>7.054</v>
       </c>
       <c r="J11" t="n">
-        <v>2626</v>
+        <v>2659</v>
       </c>
       <c r="K11" t="n">
         <v>100000000</v>
@@ -1317,7 +1317,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4.851</v>
+        <v>17.0531</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>44685</v>
@@ -1331,10 +1331,10 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>7.265</v>
+        <v>7.262</v>
       </c>
       <c r="J12" t="n">
-        <v>9399</v>
+        <v>9436</v>
       </c>
       <c r="K12" t="n">
         <v>200000000</v>
@@ -1394,7 +1394,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>7.05</v>
+        <v>28.9731</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>45126</v>
@@ -1408,10 +1408,10 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>8.1</v>
+        <v>8.066000000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>9941</v>
+        <v>10025</v>
       </c>
       <c r="K13" t="n">
         <v>100000000</v>
@@ -1471,7 +1471,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3.802</v>
+        <v>11.7687</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>44741</v>
@@ -1485,10 +1485,10 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>7.3</v>
+        <v>7.301</v>
       </c>
       <c r="J14" t="n">
-        <v>3687</v>
+        <v>3696</v>
       </c>
       <c r="K14" t="n">
         <v>85000000</v>
@@ -1548,7 +1548,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3.546</v>
+        <v>1.0514</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>44469</v>
@@ -1562,10 +1562,10 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>5.9</v>
+        <v>5.917</v>
       </c>
       <c r="J15" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="K15" t="n">
         <v>200000000</v>
@@ -1625,7 +1625,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3.888</v>
+        <v>18.8961</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>44874</v>
@@ -1639,10 +1639,10 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>7.07</v>
+        <v>7.068</v>
       </c>
       <c r="J16" t="n">
-        <v>6707</v>
+        <v>6743</v>
       </c>
       <c r="K16" t="n">
         <v>250000000</v>
@@ -1702,7 +1702,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3.875</v>
+        <v>17.6654</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>45049</v>
@@ -1716,10 +1716,10 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>7.949</v>
+        <v>7.9</v>
       </c>
       <c r="J17" t="n">
-        <v>7189</v>
+        <v>7227</v>
       </c>
       <c r="K17" t="n">
         <v>250000000</v>
@@ -1779,7 +1779,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3.544</v>
+        <v>0.6823</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>44239</v>
@@ -1793,7 +1793,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>7</v>
+        <v>7.031</v>
       </c>
       <c r="J18" t="n">
         <v>147</v>
@@ -1856,7 +1856,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4.135</v>
+        <v>9.388299999999999</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>44468</v>
@@ -1873,7 +1873,7 @@
         <v>7.4</v>
       </c>
       <c r="J19" t="n">
-        <v>6427</v>
+        <v>6456</v>
       </c>
       <c r="K19" t="n">
         <v>250000000</v>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>Inglés, Francés, Italiano, Ruso, Español</t>
+          <t>Ruso, Francés, Español, Italiano, Inglés</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -1933,7 +1933,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6.013</v>
+        <v>18.8743</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>44621</v>
@@ -1950,7 +1950,7 @@
         <v>7.7</v>
       </c>
       <c r="J20" t="n">
-        <v>10721</v>
+        <v>10771</v>
       </c>
       <c r="K20" t="n">
         <v>185000000</v>
@@ -2010,7 +2010,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4.095</v>
+        <v>13.4407</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>44748</v>
@@ -2024,10 +2024,10 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>6.421</v>
+        <v>6.42</v>
       </c>
       <c r="J21" t="n">
-        <v>7789</v>
+        <v>7825</v>
       </c>
       <c r="K21" t="n">
         <v>250000000</v>
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4.492</v>
+        <v>39.9075</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>45616</v>
@@ -2101,10 +2101,10 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>6.907</v>
+        <v>6.928</v>
       </c>
       <c r="J22" t="n">
-        <v>1927</v>
+        <v>1990</v>
       </c>
       <c r="K22" t="n">
         <v>150000000</v>
@@ -2164,7 +2164,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1.783</v>
+        <v>8.897500000000001</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>44335</v>
@@ -2181,7 +2181,7 @@
         <v>7.1</v>
       </c>
       <c r="J23" t="n">
-        <v>7298</v>
+        <v>7315</v>
       </c>
       <c r="K23" t="n">
         <v>200000000</v>
@@ -2228,7 +2228,7 @@
         <v>0</v>
       </c>
       <c r="B24" t="n">
-        <v>693134</v>
+        <v>762509</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2237,41 +2237,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Dune: Part Two</t>
+          <t>Mufasa: The Lion King</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5.664</v>
+        <v>238.3487</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>45349</v>
+        <v>45644</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Duna: Parte dos</t>
+          <t>Mufasa: El rey león</t>
         </is>
       </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>8.1</v>
+        <v>7.449</v>
       </c>
       <c r="J24" t="n">
-        <v>6418</v>
+        <v>1799</v>
       </c>
       <c r="K24" t="n">
-        <v>190000000</v>
+        <v>200000000</v>
       </c>
       <c r="L24" t="n">
-        <v>714444358</v>
+        <v>717197856</v>
       </c>
       <c r="M24" t="n">
-        <v>167</v>
+        <v>118</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Ciencia ficción, Aventura</t>
+          <t>Aventura, Familia, Animación</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Legendary Pictures</t>
+          <t>Walt Disney Pictures</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>Long live the fighters.</t>
+          <t>The story of an orphan who would be king.</t>
         </is>
       </c>
     </row>
@@ -2305,7 +2305,7 @@
         <v>0</v>
       </c>
       <c r="B25" t="n">
-        <v>385687</v>
+        <v>693134</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -2314,41 +2314,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Fast X</t>
+          <t>Dune: Part Two</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3.962</v>
+        <v>25.6541</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>45063</v>
+        <v>45349</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rápidos y furiosos X</t>
+          <t>Duna: Parte dos</t>
         </is>
       </c>
       <c r="H25" t="n">
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>7.05</v>
+        <v>8.1</v>
       </c>
       <c r="J25" t="n">
-        <v>5814</v>
+        <v>6476</v>
       </c>
       <c r="K25" t="n">
-        <v>340000000</v>
+        <v>190000000</v>
       </c>
       <c r="L25" t="n">
-        <v>704709660</v>
+        <v>714444358</v>
       </c>
       <c r="M25" t="n">
-        <v>142</v>
+        <v>167</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Acción, Crimen, Suspenso, Aventura, Misterio</t>
+          <t>Ciencia ficción, Aventura</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Universal Pictures, Original Film, One Race, Perfect Storm Entertainment</t>
+          <t>Legendary Pictures</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -2368,12 +2368,12 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>Inglés, Español</t>
+          <t>Inglés</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>The end of the road begins.</t>
+          <t>Long live the fighters.</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
         <v>0</v>
       </c>
       <c r="B26" t="n">
-        <v>762509</v>
+        <v>385687</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -2391,41 +2391,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Mufasa: The Lion King</t>
+          <t>Fast X</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>10.95</v>
+        <v>36.1685</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>45644</v>
+        <v>45063</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Mufasa: El rey león</t>
+          <t>Rápidos y furiosos X</t>
         </is>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>7.469</v>
+        <v>7.049</v>
       </c>
       <c r="J26" t="n">
-        <v>1652</v>
+        <v>5828</v>
       </c>
       <c r="K26" t="n">
-        <v>200000000</v>
+        <v>340000000</v>
       </c>
       <c r="L26" t="n">
-        <v>700197856</v>
+        <v>704709660</v>
       </c>
       <c r="M26" t="n">
-        <v>118</v>
+        <v>142</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Aventura, Familia, Animación</t>
+          <t>Acción, Crimen, Suspenso, Aventura, Misterio</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Walt Disney Pictures</t>
+          <t>Universal Pictures, Original Film, One Race, Perfect Storm Entertainment</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>Inglés</t>
+          <t>Español, Inglés</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>The story of an orphan who would be king.</t>
+          <t>The end of the road begins.</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4.741</v>
+        <v>27.0356</v>
       </c>
       <c r="F27" s="2" t="n">
         <v>45077</v>
@@ -2486,10 +2486,10 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>8.300000000000001</v>
+        <v>8.343</v>
       </c>
       <c r="J27" t="n">
-        <v>7383</v>
+        <v>7424</v>
       </c>
       <c r="K27" t="n">
         <v>100000000</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3.014</v>
+        <v>1.5593</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>44239</v>
@@ -2566,7 +2566,7 @@
         <v>5.6</v>
       </c>
       <c r="J28" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K28" t="n">
         <v>117000000</v>
@@ -2626,7 +2626,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3.558</v>
+        <v>0.8041</v>
       </c>
       <c r="F29" s="2" t="n">
         <v>44948</v>
@@ -2640,10 +2640,10 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>5.9</v>
+        <v>5.927</v>
       </c>
       <c r="J29" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3.704</v>
+        <v>15.6611</v>
       </c>
       <c r="F30" s="2" t="n">
         <v>45266</v>
@@ -2717,10 +2717,10 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>7.1</v>
+        <v>7.084</v>
       </c>
       <c r="J30" t="n">
-        <v>3795</v>
+        <v>3817</v>
       </c>
       <c r="K30" t="n">
         <v>125000000</v>
@@ -2780,7 +2780,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2.596</v>
+        <v>1.4814</v>
       </c>
       <c r="F31" s="2" t="n">
         <v>44593</v>
@@ -2794,10 +2794,10 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>6.2</v>
+        <v>6.209</v>
       </c>
       <c r="J31" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K31" t="n">
         <v>200000000</v>
@@ -2857,7 +2857,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3.845</v>
+        <v>7.075</v>
       </c>
       <c r="F32" s="2" t="n">
         <v>44948</v>
@@ -2871,10 +2871,10 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>7.278</v>
+        <v>7.279</v>
       </c>
       <c r="J32" t="n">
-        <v>599</v>
+        <v>605</v>
       </c>
       <c r="K32" t="n">
         <v>73800000</v>
@@ -2934,7 +2934,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3.962</v>
+        <v>27.3889</v>
       </c>
       <c r="F33" s="2" t="n">
         <v>45378</v>
@@ -2948,10 +2948,10 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>7.1</v>
+        <v>7.099</v>
       </c>
       <c r="J33" t="n">
-        <v>4094</v>
+        <v>4119</v>
       </c>
       <c r="K33" t="n">
         <v>150000000</v>
@@ -3011,7 +3011,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3.609</v>
+        <v>16.1477</v>
       </c>
       <c r="F34" s="2" t="n">
         <v>45064</v>
@@ -3025,10 +3025,10 @@
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>6.317</v>
+        <v>6.313</v>
       </c>
       <c r="J34" t="n">
-        <v>3015</v>
+        <v>3027</v>
       </c>
       <c r="K34" t="n">
         <v>297000000</v>
@@ -3088,7 +3088,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4.944</v>
+        <v>20.5353</v>
       </c>
       <c r="F35" s="2" t="n">
         <v>45115</v>
@@ -3102,10 +3102,10 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>7.531</v>
+        <v>7.532</v>
       </c>
       <c r="J35" t="n">
-        <v>4080</v>
+        <v>4106</v>
       </c>
       <c r="K35" t="n">
         <v>291000000</v>
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3.891</v>
+        <v>28.6923</v>
       </c>
       <c r="F36" s="2" t="n">
         <v>45353</v>
@@ -3182,7 +3182,7 @@
         <v>7.1</v>
       </c>
       <c r="J36" t="n">
-        <v>2998</v>
+        <v>3015</v>
       </c>
       <c r="K36" t="n">
         <v>80000000</v>
@@ -3242,7 +3242,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4.422</v>
+        <v>10.3945</v>
       </c>
       <c r="F37" s="2" t="n">
         <v>44120</v>
@@ -3256,10 +3256,10 @@
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>8.199999999999999</v>
+        <v>8.208</v>
       </c>
       <c r="J37" t="n">
-        <v>4034</v>
+        <v>4043</v>
       </c>
       <c r="K37" t="n">
         <v>15700000</v>
@@ -3319,7 +3319,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5.67</v>
+        <v>11.6245</v>
       </c>
       <c r="F38" s="2" t="n">
         <v>44469</v>
@@ -3333,10 +3333,10 @@
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>6.777</v>
+        <v>6.8</v>
       </c>
       <c r="J38" t="n">
-        <v>10548</v>
+        <v>10571</v>
       </c>
       <c r="K38" t="n">
         <v>110000000</v>
@@ -3369,7 +3369,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>Español, Inglés</t>
+          <t>Inglés, Español</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2.804</v>
+        <v>1.5695</v>
       </c>
       <c r="F39" s="2" t="n">
         <v>45281</v>
@@ -3410,7 +3410,7 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>6.199</v>
+        <v>6.2</v>
       </c>
       <c r="J39" t="n">
         <v>79</v>
@@ -3473,7 +3473,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4.381</v>
+        <v>19.5832</v>
       </c>
       <c r="F40" s="2" t="n">
         <v>45091</v>
@@ -3490,7 +3490,7 @@
         <v>7.618</v>
       </c>
       <c r="J40" t="n">
-        <v>4711</v>
+        <v>4734</v>
       </c>
       <c r="K40" t="n">
         <v>200000000</v>
@@ -3550,7 +3550,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>10.217</v>
+        <v>150.0364</v>
       </c>
       <c r="F41" s="2" t="n">
         <v>45645</v>
@@ -3564,10 +3564,10 @@
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>7.721</v>
+        <v>7.8</v>
       </c>
       <c r="J41" t="n">
-        <v>2188</v>
+        <v>2297</v>
       </c>
       <c r="K41" t="n">
         <v>122000000</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4.471</v>
+        <v>21.7922</v>
       </c>
       <c r="F42" s="2" t="n">
         <v>44902</v>
@@ -3641,10 +3641,10 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>8.199999999999999</v>
+        <v>8.217000000000001</v>
       </c>
       <c r="J42" t="n">
-        <v>8052</v>
+        <v>8074</v>
       </c>
       <c r="K42" t="n">
         <v>90000000</v>
@@ -3704,7 +3704,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2.705</v>
+        <v>1.6015</v>
       </c>
       <c r="F43" s="2" t="n">
         <v>45332</v>
@@ -3718,10 +3718,10 @@
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="J43" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K43" t="n">
         <v>100000000</v>
@@ -3781,7 +3781,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5.662</v>
+        <v>84.6773</v>
       </c>
       <c r="F44" s="2" t="n">
         <v>45587</v>
@@ -3795,10 +3795,10 @@
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>6.796</v>
+        <v>6.8</v>
       </c>
       <c r="J44" t="n">
-        <v>3029</v>
+        <v>3108</v>
       </c>
       <c r="K44" t="n">
         <v>120000000</v>
@@ -3858,7 +3858,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4.157</v>
+        <v>10.9634</v>
       </c>
       <c r="F45" s="2" t="n">
         <v>44972</v>
@@ -3872,10 +3872,10 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>6.3</v>
+        <v>6.295</v>
       </c>
       <c r="J45" t="n">
-        <v>5178</v>
+        <v>5201</v>
       </c>
       <c r="K45" t="n">
         <v>388369742</v>
@@ -3935,7 +3935,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2.036</v>
+        <v>1.4358</v>
       </c>
       <c r="F46" s="2" t="n">
         <v>45486</v>
@@ -3949,10 +3949,10 @@
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>7</v>
+        <v>6.964</v>
       </c>
       <c r="J46" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -4012,7 +4012,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4.082</v>
+        <v>8.297599999999999</v>
       </c>
       <c r="F47" s="2" t="n">
         <v>44279</v>
@@ -4026,10 +4026,10 @@
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>7.582</v>
+        <v>7.579</v>
       </c>
       <c r="J47" t="n">
-        <v>10113</v>
+        <v>10142</v>
       </c>
       <c r="K47" t="n">
         <v>200000000</v>
@@ -4089,7 +4089,7 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2.07</v>
+        <v>1.2248</v>
       </c>
       <c r="F48" s="2" t="n">
         <v>45332</v>
@@ -4103,10 +4103,10 @@
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>7.246</v>
+        <v>7.1</v>
       </c>
       <c r="J48" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
@@ -4166,7 +4166,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>3.792</v>
+        <v>1.8966</v>
       </c>
       <c r="F49" s="2" t="n">
         <v>44057</v>
@@ -4183,7 +4183,7 @@
         <v>6.9</v>
       </c>
       <c r="J49" t="n">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="K49" t="n">
         <v>80000000</v>
@@ -4243,7 +4243,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3.023</v>
+        <v>0.6466</v>
       </c>
       <c r="F50" s="2" t="n">
         <v>44771</v>
@@ -4260,7 +4260,7 @@
         <v>6.9</v>
       </c>
       <c r="J50" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
@@ -4320,7 +4320,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6.648</v>
+        <v>71.5954</v>
       </c>
       <c r="F51" s="2" t="n">
         <v>45609</v>
@@ -4334,10 +4334,10 @@
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>6.774</v>
+        <v>6.765</v>
       </c>
       <c r="J51" t="n">
-        <v>3033</v>
+        <v>3103</v>
       </c>
       <c r="K51" t="n">
         <v>310000000</v>
@@ -4346,7 +4346,7 @@
         <v>458718000</v>
       </c>
       <c r="M51" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="N51" t="inlineStr">
         <is>
@@ -4397,7 +4397,7 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4.748</v>
+        <v>15.2978</v>
       </c>
       <c r="F52" s="2" t="n">
         <v>45539</v>
@@ -4411,10 +4411,10 @@
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>7.045</v>
+        <v>7.042</v>
       </c>
       <c r="J52" t="n">
-        <v>2379</v>
+        <v>2405</v>
       </c>
       <c r="K52" t="n">
         <v>100000000</v>
@@ -4427,7 +4427,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>Comedia, Fantasía, Terror</t>
+          <t>Terror, Comedia, Fantasía</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -4474,7 +4474,7 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3.819</v>
+        <v>20.2842</v>
       </c>
       <c r="F53" s="2" t="n">
         <v>45083</v>
@@ -4488,10 +4488,10 @@
         <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>7.248</v>
+        <v>7.2</v>
       </c>
       <c r="J53" t="n">
-        <v>4834</v>
+        <v>4846</v>
       </c>
       <c r="K53" t="n">
         <v>195000000</v>
@@ -4551,7 +4551,7 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4.445</v>
+        <v>27.0149</v>
       </c>
       <c r="F54" s="2" t="n">
         <v>45007</v>
@@ -4568,7 +4568,7 @@
         <v>7.7</v>
       </c>
       <c r="J54" t="n">
-        <v>6896</v>
+        <v>6932</v>
       </c>
       <c r="K54" t="n">
         <v>90000000</v>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>3.679</v>
+        <v>14.852</v>
       </c>
       <c r="F55" s="2" t="n">
         <v>45280</v>
@@ -4642,10 +4642,10 @@
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>6.6</v>
+        <v>6.611</v>
       </c>
       <c r="J55" t="n">
-        <v>2992</v>
+        <v>3004</v>
       </c>
       <c r="K55" t="n">
         <v>205000000</v>
@@ -4705,7 +4705,7 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4.156</v>
+        <v>15.9028</v>
       </c>
       <c r="F56" s="2" t="n">
         <v>44440</v>
@@ -4719,10 +4719,10 @@
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>7.526</v>
+        <v>7.523</v>
       </c>
       <c r="J56" t="n">
-        <v>9600</v>
+        <v>9642</v>
       </c>
       <c r="K56" t="n">
         <v>150000000</v>
@@ -4782,7 +4782,7 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.047</v>
+        <v>0.1385</v>
       </c>
       <c r="F57" s="2" t="n">
         <v>43990</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4.622</v>
+        <v>12.3445</v>
       </c>
       <c r="F58" s="2" t="n">
         <v>43845</v>
@@ -4865,10 +4865,10 @@
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>7.135</v>
+        <v>7.134</v>
       </c>
       <c r="J58" t="n">
-        <v>8363</v>
+        <v>8373</v>
       </c>
       <c r="K58" t="n">
         <v>90000000</v>
@@ -4928,7 +4928,7 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4.086</v>
+        <v>11.9223</v>
       </c>
       <c r="F59" s="2" t="n">
         <v>44531</v>
@@ -4942,10 +4942,10 @@
         <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="J59" t="n">
-        <v>4469</v>
+        <v>4476</v>
       </c>
       <c r="K59" t="n">
         <v>85000000</v>
@@ -5005,7 +5005,7 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6.354</v>
+        <v>24.7169</v>
       </c>
       <c r="F60" s="2" t="n">
         <v>44454</v>
@@ -5022,7 +5022,7 @@
         <v>7.782</v>
       </c>
       <c r="J60" t="n">
-        <v>13304</v>
+        <v>13362</v>
       </c>
       <c r="K60" t="n">
         <v>165000000</v>
@@ -5082,7 +5082,7 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>3.867</v>
+        <v>14.9264</v>
       </c>
       <c r="F61" s="2" t="n">
         <v>44657</v>
@@ -5096,10 +5096,10 @@
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>6.647</v>
+        <v>6.6</v>
       </c>
       <c r="J61" t="n">
-        <v>4627</v>
+        <v>4650</v>
       </c>
       <c r="K61" t="n">
         <v>200000000</v>
@@ -5159,7 +5159,7 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4.402</v>
+        <v>10.6744</v>
       </c>
       <c r="F62" s="2" t="n">
         <v>44602</v>
@@ -5173,10 +5173,10 @@
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>6.916</v>
+        <v>6.913</v>
       </c>
       <c r="J62" t="n">
-        <v>6165</v>
+        <v>6194</v>
       </c>
       <c r="K62" t="n">
         <v>120000000</v>
@@ -5236,7 +5236,7 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>3.855</v>
+        <v>24.2806</v>
       </c>
       <c r="F63" s="2" t="n">
         <v>44650</v>
@@ -5250,10 +5250,10 @@
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>7.474</v>
+        <v>7.472</v>
       </c>
       <c r="J63" t="n">
-        <v>5394</v>
+        <v>5420</v>
       </c>
       <c r="K63" t="n">
         <v>110000000</v>
@@ -5313,7 +5313,7 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4.226</v>
+        <v>36.3891</v>
       </c>
       <c r="F64" s="2" t="n">
         <v>45448</v>
@@ -5327,10 +5327,10 @@
         <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>7.383</v>
+        <v>7.4</v>
       </c>
       <c r="J64" t="n">
-        <v>2795</v>
+        <v>2814</v>
       </c>
       <c r="K64" t="n">
         <v>100000000</v>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4.858</v>
+        <v>10.0214</v>
       </c>
       <c r="F65" s="2" t="n">
         <v>44503</v>
@@ -5404,10 +5404,10 @@
         <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>6.828</v>
+        <v>6.8</v>
       </c>
       <c r="J65" t="n">
-        <v>8454</v>
+        <v>8481</v>
       </c>
       <c r="K65" t="n">
         <v>200000000</v>
@@ -5467,7 +5467,7 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.028</v>
+        <v>0.0071</v>
       </c>
       <c r="F66" s="2" t="n">
         <v>44927</v>
@@ -5536,7 +5536,7 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>3.919</v>
+        <v>23.8669</v>
       </c>
       <c r="F67" s="2" t="n">
         <v>45420</v>
@@ -5550,10 +5550,10 @@
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>7.083</v>
+        <v>7.1</v>
       </c>
       <c r="J67" t="n">
-        <v>3617</v>
+        <v>3644</v>
       </c>
       <c r="K67" t="n">
         <v>160000000</v>
@@ -5613,7 +5613,7 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4.074</v>
+        <v>11.9891</v>
       </c>
       <c r="F68" s="2" t="n">
         <v>44853</v>
@@ -5630,7 +5630,7 @@
         <v>6.9</v>
       </c>
       <c r="J68" t="n">
-        <v>6461</v>
+        <v>6479</v>
       </c>
       <c r="K68" t="n">
         <v>200000000</v>
@@ -5690,7 +5690,7 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1.431</v>
+        <v>0.8423</v>
       </c>
       <c r="F69" s="2" t="n">
         <v>44593</v>
@@ -5707,7 +5707,7 @@
         <v>6.2</v>
       </c>
       <c r="J69" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K69" t="n">
         <v>0</v>
@@ -5767,7 +5767,7 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3.606</v>
+        <v>16.1703</v>
       </c>
       <c r="F70" s="2" t="n">
         <v>45140</v>
@@ -5781,10 +5781,10 @@
         <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>6.449</v>
+        <v>6.4</v>
       </c>
       <c r="J70" t="n">
-        <v>3534</v>
+        <v>3544</v>
       </c>
       <c r="K70" t="n">
         <v>129000000</v>
@@ -5844,7 +5844,7 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4.655</v>
+        <v>10.8733</v>
       </c>
       <c r="F71" s="2" t="n">
         <v>45102</v>
@@ -5858,10 +5858,10 @@
         <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>6.6</v>
+        <v>6.559</v>
       </c>
       <c r="J71" t="n">
-        <v>3579</v>
+        <v>3600</v>
       </c>
       <c r="K71" t="n">
         <v>294700000</v>
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4.137</v>
+        <v>15.8599</v>
       </c>
       <c r="F72" s="2" t="n">
         <v>44384</v>
@@ -5935,10 +5935,10 @@
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>7.212</v>
+        <v>7.2</v>
       </c>
       <c r="J72" t="n">
-        <v>10384</v>
+        <v>10415</v>
       </c>
       <c r="K72" t="n">
         <v>200000000</v>
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4.35</v>
+        <v>19.391</v>
       </c>
       <c r="F73" s="2" t="n">
         <v>45483</v>
@@ -6012,10 +6012,10 @@
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>6.857</v>
+        <v>6.856</v>
       </c>
       <c r="J73" t="n">
-        <v>2293</v>
+        <v>2336</v>
       </c>
       <c r="K73" t="n">
         <v>155000000</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>3.817</v>
+        <v>6.6178</v>
       </c>
       <c r="F74" s="2" t="n">
         <v>45122</v>
@@ -6089,10 +6089,10 @@
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>7.085</v>
+        <v>7.1</v>
       </c>
       <c r="J74" t="n">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="K74" t="n">
         <v>85000000</v>
@@ -6152,7 +6152,7 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>3.946</v>
+        <v>10.1228</v>
       </c>
       <c r="F75" s="2" t="n">
         <v>44065</v>
@@ -6166,10 +6166,10 @@
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>7.2</v>
+        <v>7.182</v>
       </c>
       <c r="J75" t="n">
-        <v>10116</v>
+        <v>10149</v>
       </c>
       <c r="K75" t="n">
         <v>205000000</v>
@@ -6229,7 +6229,7 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4.479</v>
+        <v>15.6867</v>
       </c>
       <c r="F76" s="2" t="n">
         <v>45511</v>
@@ -6243,10 +6243,10 @@
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>7.055</v>
+        <v>7.047</v>
       </c>
       <c r="J76" t="n">
-        <v>1500</v>
+        <v>1535</v>
       </c>
       <c r="K76" t="n">
         <v>25000000</v>
@@ -6306,7 +6306,7 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5.181</v>
+        <v>35.4648</v>
       </c>
       <c r="F77" s="2" t="n">
         <v>45517</v>
@@ -6320,10 +6320,10 @@
         <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>7.213</v>
+        <v>7.214</v>
       </c>
       <c r="J77" t="n">
-        <v>3434</v>
+        <v>3484</v>
       </c>
       <c r="K77" t="n">
         <v>80000000</v>
@@ -6383,7 +6383,7 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1.505</v>
+        <v>0.9338</v>
       </c>
       <c r="F78" s="2" t="n">
         <v>45332</v>
@@ -6397,10 +6397,10 @@
         <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>6.8</v>
+        <v>6.81</v>
       </c>
       <c r="J78" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K78" t="n">
         <v>0</v>
@@ -6460,7 +6460,7 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>3.845</v>
+        <v>16.8721</v>
       </c>
       <c r="F79" s="2" t="n">
         <v>45245</v>
@@ -6474,10 +6474,10 @@
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>7.031</v>
+        <v>7.027</v>
       </c>
       <c r="J79" t="n">
-        <v>2932</v>
+        <v>2960</v>
       </c>
       <c r="K79" t="n">
         <v>100000000</v>
@@ -6537,7 +6537,7 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2.965</v>
+        <v>1.1791</v>
       </c>
       <c r="F80" s="2" t="n">
         <v>45099</v>
@@ -6554,7 +6554,7 @@
         <v>6.5</v>
       </c>
       <c r="J80" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K80" t="n">
         <v>9500000</v>
@@ -6614,7 +6614,7 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>7.35</v>
+        <v>58.4281</v>
       </c>
       <c r="F81" s="2" t="n">
         <v>45547</v>
@@ -6628,10 +6628,10 @@
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>8.337999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J81" t="n">
-        <v>4538</v>
+        <v>4616</v>
       </c>
       <c r="K81" t="n">
         <v>78000000</v>
@@ -6691,7 +6691,7 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4.67</v>
+        <v>8.3955</v>
       </c>
       <c r="F82" s="2" t="n">
         <v>44419</v>
@@ -6705,10 +6705,10 @@
         <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>7.484</v>
+        <v>7.483</v>
       </c>
       <c r="J82" t="n">
-        <v>8983</v>
+        <v>9007</v>
       </c>
       <c r="K82" t="n">
         <v>110000000</v>
@@ -6768,7 +6768,7 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4.811</v>
+        <v>6.544</v>
       </c>
       <c r="F83" s="2" t="n">
         <v>44876</v>
@@ -6782,10 +6782,10 @@
         <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>7.938</v>
+        <v>7.931</v>
       </c>
       <c r="J83" t="n">
-        <v>1420</v>
+        <v>1436</v>
       </c>
       <c r="K83" t="n">
         <v>0</v>
@@ -6845,7 +6845,7 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4.113</v>
+        <v>16.5439</v>
       </c>
       <c r="F84" s="2" t="n">
         <v>43873</v>
@@ -6862,7 +6862,7 @@
         <v>7.3</v>
       </c>
       <c r="J84" t="n">
-        <v>9826</v>
+        <v>9850</v>
       </c>
       <c r="K84" t="n">
         <v>85000000</v>
@@ -6922,7 +6922,7 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>3.836</v>
+        <v>22.9018</v>
       </c>
       <c r="F85" s="2" t="n">
         <v>45266</v>
@@ -6939,7 +6939,7 @@
         <v>7.4</v>
       </c>
       <c r="J85" t="n">
-        <v>1954</v>
+        <v>1962</v>
       </c>
       <c r="K85" t="n">
         <v>72000000</v>
@@ -6999,7 +6999,7 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4.376</v>
+        <v>10.6737</v>
       </c>
       <c r="F86" s="2" t="n">
         <v>44337</v>
@@ -7013,10 +7013,10 @@
         <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>7.474</v>
+        <v>7.5</v>
       </c>
       <c r="J86" t="n">
-        <v>6712</v>
+        <v>6733</v>
       </c>
       <c r="K86" t="n">
         <v>55000000</v>
@@ -7076,7 +7076,7 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>4.624</v>
+        <v>13.6723</v>
       </c>
       <c r="F87" s="2" t="n">
         <v>45224</v>
@@ -7093,7 +7093,7 @@
         <v>7.484</v>
       </c>
       <c r="J87" t="n">
-        <v>4259</v>
+        <v>4270</v>
       </c>
       <c r="K87" t="n">
         <v>20000000</v>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>Terror, Suspenso, Misterio</t>
+          <t>Terror, Suspenso</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4.613</v>
+        <v>19.0707</v>
       </c>
       <c r="F88" s="2" t="n">
         <v>45121</v>
@@ -7167,10 +7167,10 @@
         <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>7.45</v>
+        <v>7.5</v>
       </c>
       <c r="J88" t="n">
-        <v>2067</v>
+        <v>2104</v>
       </c>
       <c r="K88" t="n">
         <v>50000000</v>
@@ -7230,7 +7230,7 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>3.852</v>
+        <v>5.6411</v>
       </c>
       <c r="F89" s="2" t="n">
         <v>44734</v>
@@ -7244,10 +7244,10 @@
         <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>7.505</v>
+        <v>7.5</v>
       </c>
       <c r="J89" t="n">
-        <v>3512</v>
+        <v>3530</v>
       </c>
       <c r="K89" t="n">
         <v>85000000</v>
@@ -7307,7 +7307,7 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.34</v>
+        <v>0.8388</v>
       </c>
       <c r="F90" s="2" t="n">
         <v>45332</v>
@@ -7384,7 +7384,7 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>3.818</v>
+        <v>8.0509</v>
       </c>
       <c r="F91" s="2" t="n">
         <v>44986</v>
@@ -7401,7 +7401,7 @@
         <v>7.1</v>
       </c>
       <c r="J91" t="n">
-        <v>2594</v>
+        <v>2603</v>
       </c>
       <c r="K91" t="n">
         <v>75000000</v>
@@ -7461,7 +7461,7 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>3.621</v>
+        <v>16.0048</v>
       </c>
       <c r="F92" s="2" t="n">
         <v>45090</v>
@@ -7475,10 +7475,10 @@
         <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>6.666</v>
+        <v>6.662</v>
       </c>
       <c r="J92" t="n">
-        <v>4439</v>
+        <v>4466</v>
       </c>
       <c r="K92" t="n">
         <v>220000000</v>
@@ -7538,7 +7538,7 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4.146</v>
+        <v>15.4765</v>
       </c>
       <c r="F93" s="2" t="n">
         <v>45175</v>
@@ -7552,10 +7552,10 @@
         <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>6.71</v>
+        <v>6.711</v>
       </c>
       <c r="J93" t="n">
-        <v>2131</v>
+        <v>2139</v>
       </c>
       <c r="K93" t="n">
         <v>38500000</v>
@@ -7615,7 +7615,7 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>4.239</v>
+        <v>24.7039</v>
       </c>
       <c r="F94" s="2" t="n">
         <v>45469</v>
@@ -7629,10 +7629,10 @@
         <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>6.7</v>
+        <v>6.741</v>
       </c>
       <c r="J94" t="n">
-        <v>2596</v>
+        <v>2656</v>
       </c>
       <c r="K94" t="n">
         <v>67000000</v>
@@ -7692,7 +7692,7 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>3.573</v>
+        <v>3.4188</v>
       </c>
       <c r="F95" s="2" t="n">
         <v>45212</v>
@@ -7706,10 +7706,10 @@
         <v>0</v>
       </c>
       <c r="I95" t="n">
-        <v>8.199999999999999</v>
+        <v>8.259</v>
       </c>
       <c r="J95" t="n">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="K95" t="n">
         <v>15000000</v>
@@ -7769,7 +7769,7 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>4.142</v>
+        <v>17.6489</v>
       </c>
       <c r="F96" s="2" t="n">
         <v>44482</v>
@@ -7786,7 +7786,7 @@
         <v>7.595</v>
       </c>
       <c r="J96" t="n">
-        <v>9639</v>
+        <v>9658</v>
       </c>
       <c r="K96" t="n">
         <v>135000000</v>
@@ -7846,7 +7846,7 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>3.829</v>
+        <v>3.9327</v>
       </c>
       <c r="F97" s="2" t="n">
         <v>44898</v>
@@ -7863,7 +7863,7 @@
         <v>7.749</v>
       </c>
       <c r="J97" t="n">
-        <v>432</v>
+        <v>443</v>
       </c>
       <c r="K97" t="n">
         <v>0</v>
@@ -7923,7 +7923,7 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>3.578</v>
+        <v>12.7589</v>
       </c>
       <c r="F98" s="2" t="n">
         <v>45243</v>
@@ -7937,10 +7937,10 @@
         <v>0</v>
       </c>
       <c r="I98" t="n">
-        <v>6.321</v>
+        <v>6.3</v>
       </c>
       <c r="J98" t="n">
-        <v>1567</v>
+        <v>1574</v>
       </c>
       <c r="K98" t="n">
         <v>175000000</v>
@@ -8000,7 +8000,7 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>3.606</v>
+        <v>23.5052</v>
       </c>
       <c r="F99" s="2" t="n">
         <v>45412</v>
@@ -8014,10 +8014,10 @@
         <v>0</v>
       </c>
       <c r="I99" t="n">
-        <v>7.078</v>
+        <v>7.1</v>
       </c>
       <c r="J99" t="n">
-        <v>1230</v>
+        <v>1232</v>
       </c>
       <c r="K99" t="n">
         <v>60000000</v>
@@ -8077,7 +8077,7 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1.364</v>
+        <v>0.2619</v>
       </c>
       <c r="F100" s="2" t="n">
         <v>44736</v>
@@ -8154,7 +8154,7 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1.695</v>
+        <v>1.3008</v>
       </c>
       <c r="F101" s="2" t="n">
         <v>45109</v>
@@ -8168,10 +8168,10 @@
         <v>0</v>
       </c>
       <c r="I101" t="n">
-        <v>7.542</v>
+        <v>7.6</v>
       </c>
       <c r="J101" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="K101" t="n">
         <v>0</v>

--- a/src/static/xlsx/cleaned_data.xlsx
+++ b/src/static/xlsx/cleaned_data.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Inglés</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>26.3784</v>
+        <v>25.4995</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>44909</v>
@@ -561,10 +561,10 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>7.607</v>
+        <v>7.608</v>
       </c>
       <c r="J2" t="n">
-        <v>12403</v>
+        <v>12427</v>
       </c>
       <c r="K2" t="n">
         <v>460000000</v>
@@ -582,7 +582,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>US</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -615,7 +615,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Inglés</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>29.0789</v>
+        <v>29.1545</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>44545</v>
@@ -638,10 +638,10 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>7.947</v>
+        <v>7.946</v>
       </c>
       <c r="J3" t="n">
-        <v>20634</v>
+        <v>20654</v>
       </c>
       <c r="K3" t="n">
         <v>200000000</v>
@@ -659,7 +659,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>US</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Inglés</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53.9804</v>
+        <v>52.8141</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>45454</v>
@@ -715,10 +715,10 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>7.557</v>
+        <v>7.556</v>
       </c>
       <c r="J4" t="n">
-        <v>5698</v>
+        <v>5713</v>
       </c>
       <c r="K4" t="n">
         <v>200000000</v>
@@ -736,7 +736,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>US</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Inglés</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -778,7 +778,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>30.1254</v>
+        <v>34.2236</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>44702</v>
@@ -792,10 +792,10 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>8.182</v>
+        <v>8.180999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>9685</v>
+        <v>9705</v>
       </c>
       <c r="K5" t="n">
         <v>170000000</v>
@@ -813,7 +813,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>US</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Inglés</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>22.6255</v>
+        <v>22.8885</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>45126</v>
@@ -869,10 +869,10 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>6.981</v>
+        <v>7</v>
       </c>
       <c r="J6" t="n">
-        <v>9730</v>
+        <v>9750</v>
       </c>
       <c r="K6" t="n">
         <v>145000000</v>
@@ -890,7 +890,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>US</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Reino Unido, Estados Unidos</t>
+          <t>United Kingdom, United States of America</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Inglés</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -932,7 +932,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>26.1428</v>
+        <v>26.3238</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>45021</v>
@@ -946,10 +946,10 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>7.626</v>
+        <v>7.6</v>
       </c>
       <c r="J7" t="n">
-        <v>9554</v>
+        <v>9568</v>
       </c>
       <c r="K7" t="n">
         <v>100000000</v>
@@ -967,7 +967,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>US</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Japón, Estados Unidos</t>
+          <t>Japan, United States of America</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Inglés</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1009,7 +1009,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>66.9084</v>
+        <v>61.4447</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>45497</v>
@@ -1023,10 +1023,10 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>7.6</v>
+        <v>7.608</v>
       </c>
       <c r="J8" t="n">
-        <v>6968</v>
+        <v>7000</v>
       </c>
       <c r="K8" t="n">
         <v>200000000</v>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>US</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Inglés</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1086,7 +1086,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220.0556</v>
+        <v>182.5604</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>45617</v>
@@ -1100,16 +1100,16 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>7.118</v>
+        <v>7.108</v>
       </c>
       <c r="J9" t="n">
-        <v>2096</v>
+        <v>2139</v>
       </c>
       <c r="K9" t="n">
         <v>150000000</v>
       </c>
       <c r="L9" t="n">
-        <v>1056396565</v>
+        <v>1059544057</v>
       </c>
       <c r="M9" t="n">
         <v>99</v>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>US</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Canadá, Estados Unidos</t>
+          <t>Canada, United States of America</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Inglés</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1163,7 +1163,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>18.5198</v>
+        <v>17.5589</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>44713</v>
@@ -1180,7 +1180,7 @@
         <v>6.7</v>
       </c>
       <c r="J10" t="n">
-        <v>6297</v>
+        <v>6303</v>
       </c>
       <c r="K10" t="n">
         <v>165000000</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>US</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Inglés</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>63.4427</v>
+        <v>62.0002</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>45463</v>
@@ -1254,10 +1254,10 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>7.054</v>
+        <v>7.051</v>
       </c>
       <c r="J11" t="n">
-        <v>2659</v>
+        <v>2668</v>
       </c>
       <c r="K11" t="n">
         <v>100000000</v>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>US</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Inglés</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1317,7 +1317,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>17.0531</v>
+        <v>17.6728</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>44685</v>
@@ -1331,10 +1331,10 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>7.262</v>
+        <v>7.264</v>
       </c>
       <c r="J12" t="n">
-        <v>9436</v>
+        <v>9452</v>
       </c>
       <c r="K12" t="n">
         <v>200000000</v>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>US</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Inglés</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1394,7 +1394,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>28.9731</v>
+        <v>30.6966</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>45126</v>
@@ -1408,10 +1408,10 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>8.066000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="J13" t="n">
-        <v>10025</v>
+        <v>10057</v>
       </c>
       <c r="K13" t="n">
         <v>100000000</v>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>US</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Reino Unido, Estados Unidos</t>
+          <t>United Kingdom, United States of America</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Inglés</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1471,7 +1471,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>11.7687</v>
+        <v>11.6528</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>44741</v>
@@ -1485,10 +1485,10 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>7.301</v>
+        <v>7.3</v>
       </c>
       <c r="J14" t="n">
-        <v>3696</v>
+        <v>3699</v>
       </c>
       <c r="K14" t="n">
         <v>85000000</v>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>US</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1516,7 +1516,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chino</t>
+          <t>zh</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1548,7 +1548,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1.0514</v>
+        <v>1.242</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>44469</v>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Inglés</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1625,7 +1625,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>18.8961</v>
+        <v>17.1932</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>44874</v>
@@ -1639,10 +1639,10 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>7.068</v>
+        <v>7.067</v>
       </c>
       <c r="J16" t="n">
-        <v>6743</v>
+        <v>6756</v>
       </c>
       <c r="K16" t="n">
         <v>250000000</v>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>US</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Inglés</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1702,7 +1702,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>17.6654</v>
+        <v>17.562</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>45049</v>
@@ -1716,10 +1716,10 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>7.9</v>
+        <v>7.948</v>
       </c>
       <c r="J17" t="n">
-        <v>7227</v>
+        <v>7242</v>
       </c>
       <c r="K17" t="n">
         <v>250000000</v>
@@ -1737,7 +1737,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>US</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chino</t>
+          <t>zh</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1779,7 +1779,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.6823</v>
+        <v>0.7501</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>44239</v>
@@ -1814,7 +1814,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Inglés</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1856,7 +1856,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>9.388299999999999</v>
+        <v>10.1007</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>44468</v>
@@ -1870,10 +1870,10 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>7.4</v>
+        <v>7.365</v>
       </c>
       <c r="J19" t="n">
-        <v>6456</v>
+        <v>6463</v>
       </c>
       <c r="K19" t="n">
         <v>250000000</v>
@@ -1891,7 +1891,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Reino Unido, Estados Unidos</t>
+          <t>United Kingdom, United States of America</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Inglés</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1933,7 +1933,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>18.8743</v>
+        <v>20.5049</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>44621</v>
@@ -1947,10 +1947,10 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>7.7</v>
+        <v>7.655</v>
       </c>
       <c r="J20" t="n">
-        <v>10771</v>
+        <v>10785</v>
       </c>
       <c r="K20" t="n">
         <v>185000000</v>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>US</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Inglés</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2010,7 +2010,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>13.4407</v>
+        <v>14.6281</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>44748</v>
@@ -2027,7 +2027,7 @@
         <v>6.42</v>
       </c>
       <c r="J21" t="n">
-        <v>7825</v>
+        <v>7836</v>
       </c>
       <c r="K21" t="n">
         <v>250000000</v>
@@ -2045,7 +2045,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>US</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2078,7 +2078,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Inglés</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>39.9075</v>
+        <v>39.5869</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>45616</v>
@@ -2101,16 +2101,16 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>6.928</v>
+        <v>6.933</v>
       </c>
       <c r="J22" t="n">
-        <v>1990</v>
+        <v>2014</v>
       </c>
       <c r="K22" t="n">
         <v>150000000</v>
       </c>
       <c r="L22" t="n">
-        <v>728145850</v>
+        <v>747289164</v>
       </c>
       <c r="M22" t="n">
         <v>162</v>
@@ -2122,7 +2122,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>US</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Inglés</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2164,7 +2164,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>8.897500000000001</v>
+        <v>8.6699</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>44335</v>
@@ -2178,10 +2178,10 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>7.1</v>
+        <v>7.054</v>
       </c>
       <c r="J23" t="n">
-        <v>7315</v>
+        <v>7325</v>
       </c>
       <c r="K23" t="n">
         <v>200000000</v>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>US</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2209,7 +2209,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Inglés</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2241,7 +2241,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>238.3487</v>
+        <v>181.448</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>45644</v>
@@ -2255,16 +2255,16 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>7.449</v>
+        <v>7.444</v>
       </c>
       <c r="J24" t="n">
-        <v>1799</v>
+        <v>1862</v>
       </c>
       <c r="K24" t="n">
         <v>200000000</v>
       </c>
       <c r="L24" t="n">
-        <v>717197856</v>
+        <v>721046090</v>
       </c>
       <c r="M24" t="n">
         <v>118</v>
@@ -2276,7 +2276,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>US</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2309,7 +2309,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Inglés</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2318,7 +2318,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>25.6541</v>
+        <v>28.2372</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>45349</v>
@@ -2335,7 +2335,7 @@
         <v>8.1</v>
       </c>
       <c r="J25" t="n">
-        <v>6476</v>
+        <v>6494</v>
       </c>
       <c r="K25" t="n">
         <v>190000000</v>
@@ -2353,7 +2353,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>US</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -2363,7 +2363,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Inglés</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2395,7 +2395,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>36.1685</v>
+        <v>35.6408</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>45063</v>
@@ -2412,7 +2412,7 @@
         <v>7.049</v>
       </c>
       <c r="J26" t="n">
-        <v>5828</v>
+        <v>5834</v>
       </c>
       <c r="K26" t="n">
         <v>340000000</v>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>US</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Inglés</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2472,7 +2472,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>27.0356</v>
+        <v>29.7516</v>
       </c>
       <c r="F27" s="2" t="n">
         <v>45077</v>
@@ -2486,10 +2486,10 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>8.343</v>
+        <v>8.345000000000001</v>
       </c>
       <c r="J27" t="n">
-        <v>7424</v>
+        <v>7450</v>
       </c>
       <c r="K27" t="n">
         <v>100000000</v>
@@ -2507,7 +2507,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>US</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -2517,7 +2517,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chino</t>
+          <t>zh</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1.5593</v>
+        <v>1.4777</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>44239</v>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chino</t>
+          <t>zh</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2626,7 +2626,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.8041</v>
+        <v>0.8331</v>
       </c>
       <c r="F29" s="2" t="n">
         <v>44948</v>
@@ -2661,7 +2661,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -2694,7 +2694,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Inglés</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>15.6611</v>
+        <v>16.6254</v>
       </c>
       <c r="F30" s="2" t="n">
         <v>45266</v>
@@ -2717,16 +2717,16 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>7.084</v>
+        <v>7.086</v>
       </c>
       <c r="J30" t="n">
-        <v>3817</v>
+        <v>3823</v>
       </c>
       <c r="K30" t="n">
         <v>125000000</v>
       </c>
       <c r="L30" t="n">
-        <v>632302312</v>
+        <v>634502312</v>
       </c>
       <c r="M30" t="n">
         <v>117</v>
@@ -2738,7 +2738,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>Reino Unido, Estados Unidos</t>
+          <t>United Kingdom, United States of America</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chino</t>
+          <t>zh</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2780,7 +2780,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1.4814</v>
+        <v>1.6006</v>
       </c>
       <c r="F31" s="2" t="n">
         <v>44593</v>
@@ -2815,7 +2815,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Chino</t>
+          <t>zh</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2857,7 +2857,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>7.075</v>
+        <v>6.957</v>
       </c>
       <c r="F32" s="2" t="n">
         <v>44948</v>
@@ -2871,10 +2871,10 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>7.279</v>
+        <v>7.278</v>
       </c>
       <c r="J32" t="n">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="K32" t="n">
         <v>73800000</v>
@@ -2892,7 +2892,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Inglés</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2934,7 +2934,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>27.3889</v>
+        <v>29.6085</v>
       </c>
       <c r="F33" s="2" t="n">
         <v>45378</v>
@@ -2948,10 +2948,10 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>7.099</v>
+        <v>7.1</v>
       </c>
       <c r="J33" t="n">
-        <v>4119</v>
+        <v>4132</v>
       </c>
       <c r="K33" t="n">
         <v>150000000</v>
@@ -2969,7 +2969,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>US</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Inglés</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3011,7 +3011,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>16.1477</v>
+        <v>16.313</v>
       </c>
       <c r="F34" s="2" t="n">
         <v>45064</v>
@@ -3025,10 +3025,10 @@
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>6.313</v>
+        <v>6.318</v>
       </c>
       <c r="J34" t="n">
-        <v>3027</v>
+        <v>3033</v>
       </c>
       <c r="K34" t="n">
         <v>297000000</v>
@@ -3046,7 +3046,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>US</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Inglés</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3088,7 +3088,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>20.5353</v>
+        <v>20.4182</v>
       </c>
       <c r="F35" s="2" t="n">
         <v>45115</v>
@@ -3102,10 +3102,10 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>7.532</v>
+        <v>7.533</v>
       </c>
       <c r="J35" t="n">
-        <v>4106</v>
+        <v>4116</v>
       </c>
       <c r="K35" t="n">
         <v>291000000</v>
@@ -3123,7 +3123,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>US</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Inglés</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>28.6923</v>
+        <v>27.4675</v>
       </c>
       <c r="F36" s="2" t="n">
         <v>45353</v>
@@ -3182,7 +3182,7 @@
         <v>7.1</v>
       </c>
       <c r="J36" t="n">
-        <v>3015</v>
+        <v>3021</v>
       </c>
       <c r="K36" t="n">
         <v>80000000</v>
@@ -3200,7 +3200,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>US</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Japonés</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3242,7 +3242,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>10.3945</v>
+        <v>11.8575</v>
       </c>
       <c r="F37" s="2" t="n">
         <v>44120</v>
@@ -3256,10 +3256,10 @@
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>8.208</v>
+        <v>8.209</v>
       </c>
       <c r="J37" t="n">
-        <v>4043</v>
+        <v>4051</v>
       </c>
       <c r="K37" t="n">
         <v>15700000</v>
@@ -3277,7 +3277,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Japón</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>Japón</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Inglés</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3319,7 +3319,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>11.6245</v>
+        <v>12.5949</v>
       </c>
       <c r="F38" s="2" t="n">
         <v>44469</v>
@@ -3336,7 +3336,7 @@
         <v>6.8</v>
       </c>
       <c r="J38" t="n">
-        <v>10571</v>
+        <v>10577</v>
       </c>
       <c r="K38" t="n">
         <v>110000000</v>
@@ -3354,7 +3354,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>US</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>It’s time to meet Carnage.</t>
+          <t>You are what you eat.</t>
         </is>
       </c>
     </row>
@@ -3387,7 +3387,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>hi</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1.5695</v>
+        <v>4.0423</v>
       </c>
       <c r="F39" s="2" t="n">
         <v>45281</v>
@@ -3431,7 +3431,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -3464,7 +3464,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Inglés</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3473,7 +3473,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>19.5832</v>
+        <v>21.0991</v>
       </c>
       <c r="F40" s="2" t="n">
         <v>45091</v>
@@ -3490,7 +3490,7 @@
         <v>7.618</v>
       </c>
       <c r="J40" t="n">
-        <v>4734</v>
+        <v>4743</v>
       </c>
       <c r="K40" t="n">
         <v>200000000</v>
@@ -3508,7 +3508,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>US</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Inglés</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3550,7 +3550,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>150.0364</v>
+        <v>145.4634</v>
       </c>
       <c r="F41" s="2" t="n">
         <v>45645</v>
@@ -3567,7 +3567,7 @@
         <v>7.8</v>
       </c>
       <c r="J41" t="n">
-        <v>2297</v>
+        <v>2331</v>
       </c>
       <c r="K41" t="n">
         <v>122000000</v>
@@ -3585,7 +3585,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>US</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>Estados Unidos, Japón</t>
+          <t>United States of America, Japan</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Inglés</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>21.7922</v>
+        <v>26.2224</v>
       </c>
       <c r="F42" s="2" t="n">
         <v>44902</v>
@@ -3644,7 +3644,7 @@
         <v>8.217000000000001</v>
       </c>
       <c r="J42" t="n">
-        <v>8074</v>
+        <v>8089</v>
       </c>
       <c r="K42" t="n">
         <v>90000000</v>
@@ -3662,7 +3662,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>US</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -3672,7 +3672,7 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -3695,7 +3695,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chino</t>
+          <t>zh</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3704,7 +3704,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1.6015</v>
+        <v>1.6384</v>
       </c>
       <c r="F43" s="2" t="n">
         <v>45332</v>
@@ -3718,10 +3718,10 @@
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>6.4</v>
+        <v>6.385</v>
       </c>
       <c r="J43" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K43" t="n">
         <v>100000000</v>
@@ -3739,7 +3739,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -3772,7 +3772,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Inglés</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3781,7 +3781,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>84.6773</v>
+        <v>79.9906</v>
       </c>
       <c r="F44" s="2" t="n">
         <v>45587</v>
@@ -3795,10 +3795,10 @@
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>6.8</v>
+        <v>6.786</v>
       </c>
       <c r="J44" t="n">
-        <v>3108</v>
+        <v>3126</v>
       </c>
       <c r="K44" t="n">
         <v>120000000</v>
@@ -3816,7 +3816,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>US</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -3849,7 +3849,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Inglés</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3858,7 +3858,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>10.9634</v>
+        <v>10.6881</v>
       </c>
       <c r="F45" s="2" t="n">
         <v>44972</v>
@@ -3872,10 +3872,10 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>6.295</v>
+        <v>6.294</v>
       </c>
       <c r="J45" t="n">
-        <v>5201</v>
+        <v>5212</v>
       </c>
       <c r="K45" t="n">
         <v>388369742</v>
@@ -3893,7 +3893,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>US</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -3903,7 +3903,7 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chino</t>
+          <t>zh</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3935,7 +3935,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1.4358</v>
+        <v>1.5794</v>
       </c>
       <c r="F46" s="2" t="n">
         <v>45486</v>
@@ -3949,10 +3949,10 @@
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>6.964</v>
+        <v>6.965</v>
       </c>
       <c r="J46" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -4003,7 +4003,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Inglés</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -4012,7 +4012,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>8.297599999999999</v>
+        <v>8.9861</v>
       </c>
       <c r="F47" s="2" t="n">
         <v>44279</v>
@@ -4026,10 +4026,10 @@
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>7.579</v>
+        <v>7.578</v>
       </c>
       <c r="J47" t="n">
-        <v>10142</v>
+        <v>10152</v>
       </c>
       <c r="K47" t="n">
         <v>200000000</v>
@@ -4047,7 +4047,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>US</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -4057,7 +4057,7 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -4080,7 +4080,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chino</t>
+          <t>zh</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -4089,7 +4089,7 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1.2248</v>
+        <v>0.9452</v>
       </c>
       <c r="F48" s="2" t="n">
         <v>45332</v>
@@ -4124,7 +4124,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -4157,7 +4157,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chino</t>
+          <t>zh</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -4166,7 +4166,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1.8966</v>
+        <v>1.9397</v>
       </c>
       <c r="F49" s="2" t="n">
         <v>44057</v>
@@ -4201,7 +4201,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chino</t>
+          <t>zh</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -4243,7 +4243,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.6466</v>
+        <v>0.6876</v>
       </c>
       <c r="F50" s="2" t="n">
         <v>44771</v>
@@ -4278,7 +4278,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Inglés</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -4320,7 +4320,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>71.5954</v>
+        <v>71.5707</v>
       </c>
       <c r="F51" s="2" t="n">
         <v>45609</v>
@@ -4334,10 +4334,10 @@
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>6.765</v>
+        <v>6.8</v>
       </c>
       <c r="J51" t="n">
-        <v>3103</v>
+        <v>3137</v>
       </c>
       <c r="K51" t="n">
         <v>310000000</v>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>US</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -4365,7 +4365,7 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Inglés</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -4397,7 +4397,7 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>15.2978</v>
+        <v>16.9929</v>
       </c>
       <c r="F52" s="2" t="n">
         <v>45539</v>
@@ -4414,7 +4414,7 @@
         <v>7.042</v>
       </c>
       <c r="J52" t="n">
-        <v>2405</v>
+        <v>2421</v>
       </c>
       <c r="K52" t="n">
         <v>100000000</v>
@@ -4432,7 +4432,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>US</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -4465,7 +4465,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Inglés</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4474,7 +4474,7 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>20.2842</v>
+        <v>21.5374</v>
       </c>
       <c r="F53" s="2" t="n">
         <v>45083</v>
@@ -4488,10 +4488,10 @@
         <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>7.2</v>
+        <v>7.246</v>
       </c>
       <c r="J53" t="n">
-        <v>4846</v>
+        <v>4857</v>
       </c>
       <c r="K53" t="n">
         <v>195000000</v>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>US</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Inglés</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -4551,7 +4551,7 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>27.0149</v>
+        <v>27.9022</v>
       </c>
       <c r="F54" s="2" t="n">
         <v>45007</v>
@@ -4565,10 +4565,10 @@
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>7.7</v>
+        <v>7.722</v>
       </c>
       <c r="J54" t="n">
-        <v>6932</v>
+        <v>6950</v>
       </c>
       <c r="K54" t="n">
         <v>90000000</v>
@@ -4586,7 +4586,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>US</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>Alemania, Estados Unidos</t>
+          <t>Germany, United States of America</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -4619,7 +4619,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Inglés</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>14.852</v>
+        <v>13.0406</v>
       </c>
       <c r="F55" s="2" t="n">
         <v>45280</v>
@@ -4645,7 +4645,7 @@
         <v>6.611</v>
       </c>
       <c r="J55" t="n">
-        <v>3004</v>
+        <v>3012</v>
       </c>
       <c r="K55" t="n">
         <v>205000000</v>
@@ -4663,7 +4663,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>US</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -4673,7 +4673,7 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Inglés</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -4705,7 +4705,7 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>15.9028</v>
+        <v>17.2084</v>
       </c>
       <c r="F56" s="2" t="n">
         <v>44440</v>
@@ -4719,10 +4719,10 @@
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>7.523</v>
+        <v>7.524</v>
       </c>
       <c r="J56" t="n">
-        <v>9642</v>
+        <v>9649</v>
       </c>
       <c r="K56" t="n">
         <v>150000000</v>
@@ -4735,12 +4735,12 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>Acción, Aventura, Fantasía</t>
+          <t>Acción, Aventura, Fantasía, Ciencia ficción</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>US</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -4750,7 +4750,7 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
@@ -4773,7 +4773,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Inglés</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -4782,7 +4782,7 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.1385</v>
+        <v>0.2174</v>
       </c>
       <c r="F57" s="2" t="n">
         <v>43990</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>US</t>
         </is>
       </c>
       <c r="P57" t="inlineStr"/>
@@ -4842,7 +4842,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Inglés</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>12.3445</v>
+        <v>11.5159</v>
       </c>
       <c r="F58" s="2" t="n">
         <v>43845</v>
@@ -4865,10 +4865,10 @@
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>7.134</v>
+        <v>7.133</v>
       </c>
       <c r="J58" t="n">
-        <v>8373</v>
+        <v>8377</v>
       </c>
       <c r="K58" t="n">
         <v>90000000</v>
@@ -4886,7 +4886,7 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>US</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
@@ -4919,7 +4919,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Inglés</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -4928,7 +4928,7 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>11.9223</v>
+        <v>12.8573</v>
       </c>
       <c r="F59" s="2" t="n">
         <v>44531</v>
@@ -4942,10 +4942,10 @@
         <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>7.8</v>
+        <v>7.85</v>
       </c>
       <c r="J59" t="n">
-        <v>4476</v>
+        <v>4482</v>
       </c>
       <c r="K59" t="n">
         <v>85000000</v>
@@ -4963,7 +4963,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>US</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -4973,7 +4973,7 @@
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
@@ -4996,7 +4996,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Inglés</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -5005,7 +5005,7 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>24.7169</v>
+        <v>27.0622</v>
       </c>
       <c r="F60" s="2" t="n">
         <v>44454</v>
@@ -5022,7 +5022,7 @@
         <v>7.782</v>
       </c>
       <c r="J60" t="n">
-        <v>13362</v>
+        <v>13377</v>
       </c>
       <c r="K60" t="n">
         <v>165000000</v>
@@ -5040,7 +5040,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>US</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -5050,7 +5050,7 @@
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
@@ -5073,7 +5073,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Inglés</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -5082,7 +5082,7 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>14.9264</v>
+        <v>10.4699</v>
       </c>
       <c r="F61" s="2" t="n">
         <v>44657</v>
@@ -5096,10 +5096,10 @@
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>6.6</v>
+        <v>6.647</v>
       </c>
       <c r="J61" t="n">
-        <v>4650</v>
+        <v>4654</v>
       </c>
       <c r="K61" t="n">
         <v>200000000</v>
@@ -5117,7 +5117,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Estados Unidos, Reino Unido</t>
+          <t>US, GB</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -5127,7 +5127,7 @@
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>Reino Unido, Estados Unidos</t>
+          <t>United Kingdom, United States of America</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
@@ -5150,7 +5150,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Inglés</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -5159,7 +5159,7 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>10.6744</v>
+        <v>10.9606</v>
       </c>
       <c r="F62" s="2" t="n">
         <v>44602</v>
@@ -5173,10 +5173,10 @@
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>6.913</v>
+        <v>6.9</v>
       </c>
       <c r="J62" t="n">
-        <v>6194</v>
+        <v>6201</v>
       </c>
       <c r="K62" t="n">
         <v>120000000</v>
@@ -5194,7 +5194,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>US</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -5204,7 +5204,7 @@
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
@@ -5227,7 +5227,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Inglés</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -5236,7 +5236,7 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>24.2806</v>
+        <v>21.1506</v>
       </c>
       <c r="F63" s="2" t="n">
         <v>44650</v>
@@ -5250,10 +5250,10 @@
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>7.472</v>
+        <v>7.47</v>
       </c>
       <c r="J63" t="n">
-        <v>5420</v>
+        <v>5431</v>
       </c>
       <c r="K63" t="n">
         <v>110000000</v>
@@ -5271,7 +5271,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>US</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>Japón, Estados Unidos</t>
+          <t>Japan, United States of America</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
@@ -5304,7 +5304,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Inglés</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -5313,7 +5313,7 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>36.3891</v>
+        <v>33.9148</v>
       </c>
       <c r="F64" s="2" t="n">
         <v>45448</v>
@@ -5327,10 +5327,10 @@
         <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>7.4</v>
+        <v>7.384</v>
       </c>
       <c r="J64" t="n">
-        <v>2814</v>
+        <v>2824</v>
       </c>
       <c r="K64" t="n">
         <v>100000000</v>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>US</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -5358,7 +5358,7 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Inglés</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>10.0214</v>
+        <v>13.9837</v>
       </c>
       <c r="F65" s="2" t="n">
         <v>44503</v>
@@ -5404,10 +5404,10 @@
         <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>6.8</v>
+        <v>6.824</v>
       </c>
       <c r="J65" t="n">
-        <v>8481</v>
+        <v>8490</v>
       </c>
       <c r="K65" t="n">
         <v>200000000</v>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>US</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
@@ -5458,7 +5458,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Inglés</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -5467,7 +5467,7 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.0071</v>
+        <v>0.0658</v>
       </c>
       <c r="F66" s="2" t="n">
         <v>44927</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>US</t>
         </is>
       </c>
       <c r="P66" t="inlineStr"/>
@@ -5527,7 +5527,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Inglés</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -5536,7 +5536,7 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>23.8669</v>
+        <v>21.8199</v>
       </c>
       <c r="F67" s="2" t="n">
         <v>45420</v>
@@ -5550,10 +5550,10 @@
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>7.1</v>
+        <v>7.082</v>
       </c>
       <c r="J67" t="n">
-        <v>3644</v>
+        <v>3655</v>
       </c>
       <c r="K67" t="n">
         <v>160000000</v>
@@ -5571,7 +5571,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>US</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -5581,7 +5581,7 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
@@ -5604,7 +5604,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Inglés</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -5613,7 +5613,7 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>11.9891</v>
+        <v>11.0667</v>
       </c>
       <c r="F68" s="2" t="n">
         <v>44853</v>
@@ -5630,7 +5630,7 @@
         <v>6.9</v>
       </c>
       <c r="J68" t="n">
-        <v>6479</v>
+        <v>6486</v>
       </c>
       <c r="K68" t="n">
         <v>200000000</v>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>US</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -5658,7 +5658,7 @@
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
@@ -5681,7 +5681,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Chino</t>
+          <t>zh</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -5690,7 +5690,7 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.8423</v>
+        <v>0.5366</v>
       </c>
       <c r="F69" s="2" t="n">
         <v>44593</v>
@@ -5725,7 +5725,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Inglés</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -5767,7 +5767,7 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>16.1703</v>
+        <v>14.1558</v>
       </c>
       <c r="F70" s="2" t="n">
         <v>45140</v>
@@ -5781,10 +5781,10 @@
         <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="J70" t="n">
-        <v>3544</v>
+        <v>3547</v>
       </c>
       <c r="K70" t="n">
         <v>129000000</v>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>US</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>China, Estados Unidos</t>
+          <t>China, United States of America</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
@@ -5835,7 +5835,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Inglés</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -5844,7 +5844,7 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>10.8733</v>
+        <v>13.5364</v>
       </c>
       <c r="F71" s="2" t="n">
         <v>45102</v>
@@ -5858,10 +5858,10 @@
         <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>6.559</v>
+        <v>6.557</v>
       </c>
       <c r="J71" t="n">
-        <v>3600</v>
+        <v>3607</v>
       </c>
       <c r="K71" t="n">
         <v>294700000</v>
@@ -5879,7 +5879,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>US</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -5889,7 +5889,7 @@
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
@@ -5912,7 +5912,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Inglés</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>15.8599</v>
+        <v>13.7094</v>
       </c>
       <c r="F72" s="2" t="n">
         <v>44384</v>
@@ -5935,10 +5935,10 @@
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>7.2</v>
+        <v>7.209</v>
       </c>
       <c r="J72" t="n">
-        <v>10415</v>
+        <v>10423</v>
       </c>
       <c r="K72" t="n">
         <v>200000000</v>
@@ -5956,7 +5956,7 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>US</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
@@ -5989,7 +5989,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Inglés</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>19.391</v>
+        <v>14.2341</v>
       </c>
       <c r="F73" s="2" t="n">
         <v>45483</v>
@@ -6012,10 +6012,10 @@
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>6.856</v>
+        <v>6.855</v>
       </c>
       <c r="J73" t="n">
-        <v>2336</v>
+        <v>2351</v>
       </c>
       <c r="K73" t="n">
         <v>155000000</v>
@@ -6033,7 +6033,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>US</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
@@ -6066,7 +6066,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Chino</t>
+          <t>zh</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6.6178</v>
+        <v>7.1543</v>
       </c>
       <c r="F74" s="2" t="n">
         <v>45122</v>
@@ -6110,7 +6110,7 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Inglés</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -6152,7 +6152,7 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>10.1228</v>
+        <v>11.381</v>
       </c>
       <c r="F75" s="2" t="n">
         <v>44065</v>
@@ -6169,7 +6169,7 @@
         <v>7.182</v>
       </c>
       <c r="J75" t="n">
-        <v>10149</v>
+        <v>10165</v>
       </c>
       <c r="K75" t="n">
         <v>205000000</v>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>Estados Unidos, Reino Unido</t>
+          <t>US, GB</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -6197,7 +6197,7 @@
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>Reino Unido, Estados Unidos</t>
+          <t>United Kingdom, United States of America</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
@@ -6220,7 +6220,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Inglés</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -6229,7 +6229,7 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>15.6867</v>
+        <v>12.7934</v>
       </c>
       <c r="F76" s="2" t="n">
         <v>45511</v>
@@ -6243,10 +6243,10 @@
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>7.047</v>
+        <v>7</v>
       </c>
       <c r="J76" t="n">
-        <v>1535</v>
+        <v>1540</v>
       </c>
       <c r="K76" t="n">
         <v>25000000</v>
@@ -6264,7 +6264,7 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>US</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -6274,7 +6274,7 @@
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
@@ -6297,7 +6297,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Inglés</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -6306,7 +6306,7 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>35.4648</v>
+        <v>30.168</v>
       </c>
       <c r="F77" s="2" t="n">
         <v>45517</v>
@@ -6320,10 +6320,10 @@
         <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>7.214</v>
+        <v>7.2</v>
       </c>
       <c r="J77" t="n">
-        <v>3484</v>
+        <v>3494</v>
       </c>
       <c r="K77" t="n">
         <v>80000000</v>
@@ -6341,7 +6341,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>US</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -6351,7 +6351,7 @@
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
@@ -6374,7 +6374,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Chino</t>
+          <t>zh</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -6383,7 +6383,7 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.9338</v>
+        <v>0.5011</v>
       </c>
       <c r="F78" s="2" t="n">
         <v>45332</v>
@@ -6418,7 +6418,7 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -6451,7 +6451,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Inglés</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -6460,7 +6460,7 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>16.8721</v>
+        <v>16.3521</v>
       </c>
       <c r="F79" s="2" t="n">
         <v>45245</v>
@@ -6474,10 +6474,10 @@
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>7.027</v>
+        <v>7.028</v>
       </c>
       <c r="J79" t="n">
-        <v>2960</v>
+        <v>2970</v>
       </c>
       <c r="K79" t="n">
         <v>100000000</v>
@@ -6495,7 +6495,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>US</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -6505,7 +6505,7 @@
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>Alemania, Estados Unidos</t>
+          <t>Germany, United States of America</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
@@ -6528,7 +6528,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Chino</t>
+          <t>zh</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -6537,7 +6537,7 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1.1791</v>
+        <v>1.3477</v>
       </c>
       <c r="F80" s="2" t="n">
         <v>45099</v>
@@ -6572,7 +6572,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -6605,7 +6605,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Inglés</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -6614,7 +6614,7 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>58.4281</v>
+        <v>61.569</v>
       </c>
       <c r="F81" s="2" t="n">
         <v>45547</v>
@@ -6628,10 +6628,10 @@
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>8.300000000000001</v>
+        <v>8.333</v>
       </c>
       <c r="J81" t="n">
-        <v>4616</v>
+        <v>4646</v>
       </c>
       <c r="K81" t="n">
         <v>78000000</v>
@@ -6649,7 +6649,7 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>US</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -6659,7 +6659,7 @@
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
@@ -6682,7 +6682,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Inglés</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -6691,7 +6691,7 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>8.3955</v>
+        <v>9.32</v>
       </c>
       <c r="F82" s="2" t="n">
         <v>44419</v>
@@ -6705,10 +6705,10 @@
         <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>7.483</v>
+        <v>7.482</v>
       </c>
       <c r="J82" t="n">
-        <v>9007</v>
+        <v>9015</v>
       </c>
       <c r="K82" t="n">
         <v>110000000</v>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>US</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -6736,7 +6736,7 @@
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
@@ -6759,7 +6759,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Japonés</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -6768,7 +6768,7 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6.544</v>
+        <v>7.207</v>
       </c>
       <c r="F83" s="2" t="n">
         <v>44876</v>
@@ -6782,10 +6782,10 @@
         <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>7.931</v>
+        <v>7.927</v>
       </c>
       <c r="J83" t="n">
-        <v>1436</v>
+        <v>1443</v>
       </c>
       <c r="K83" t="n">
         <v>0</v>
@@ -6803,7 +6803,7 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>Japón</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -6813,7 +6813,7 @@
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>Japón</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
@@ -6836,7 +6836,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Inglés</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -6845,7 +6845,7 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>16.5439</v>
+        <v>17.529</v>
       </c>
       <c r="F84" s="2" t="n">
         <v>43873</v>
@@ -6862,7 +6862,7 @@
         <v>7.3</v>
       </c>
       <c r="J84" t="n">
-        <v>9850</v>
+        <v>9854</v>
       </c>
       <c r="K84" t="n">
         <v>85000000</v>
@@ -6880,7 +6880,7 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>US</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -6890,7 +6890,7 @@
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>Japón, Estados Unidos</t>
+          <t>Japan, United States of America</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
@@ -6913,7 +6913,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Inglés</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -6922,7 +6922,7 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>22.9018</v>
+        <v>23.5713</v>
       </c>
       <c r="F85" s="2" t="n">
         <v>45266</v>
@@ -6939,7 +6939,7 @@
         <v>7.4</v>
       </c>
       <c r="J85" t="n">
-        <v>1962</v>
+        <v>1966</v>
       </c>
       <c r="K85" t="n">
         <v>72000000</v>
@@ -6957,7 +6957,7 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>US</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -6967,7 +6967,7 @@
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
@@ -6990,7 +6990,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Inglés</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -6999,7 +6999,7 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>10.6737</v>
+        <v>9.8797</v>
       </c>
       <c r="F86" s="2" t="n">
         <v>44337</v>
@@ -7013,10 +7013,10 @@
         <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>7.5</v>
+        <v>7.473</v>
       </c>
       <c r="J86" t="n">
-        <v>6733</v>
+        <v>6738</v>
       </c>
       <c r="K86" t="n">
         <v>55000000</v>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>US</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -7044,7 +7044,7 @@
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
@@ -7067,7 +7067,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Inglés</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -7076,7 +7076,7 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>13.6723</v>
+        <v>29.3498</v>
       </c>
       <c r="F87" s="2" t="n">
         <v>45224</v>
@@ -7090,10 +7090,10 @@
         <v>0</v>
       </c>
       <c r="I87" t="n">
-        <v>7.484</v>
+        <v>7.483</v>
       </c>
       <c r="J87" t="n">
-        <v>4270</v>
+        <v>4279</v>
       </c>
       <c r="K87" t="n">
         <v>20000000</v>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>US</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -7121,7 +7121,7 @@
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
@@ -7144,7 +7144,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Japonés</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>19.0707</v>
+        <v>17.6106</v>
       </c>
       <c r="F88" s="2" t="n">
         <v>45121</v>
@@ -7167,10 +7167,10 @@
         <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>7.5</v>
+        <v>7.453</v>
       </c>
       <c r="J88" t="n">
-        <v>2104</v>
+        <v>2115</v>
       </c>
       <c r="K88" t="n">
         <v>50000000</v>
@@ -7188,7 +7188,7 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>Japón</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>Japón</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Inglés</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -7230,7 +7230,7 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5.6411</v>
+        <v>5.8518</v>
       </c>
       <c r="F89" s="2" t="n">
         <v>44734</v>
@@ -7247,7 +7247,7 @@
         <v>7.5</v>
       </c>
       <c r="J89" t="n">
-        <v>3530</v>
+        <v>3535</v>
       </c>
       <c r="K89" t="n">
         <v>85000000</v>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>Australia, Estados Unidos</t>
+          <t>AU, US</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -7275,7 +7275,7 @@
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>Australia, Estados Unidos</t>
+          <t>Australia, United States of America</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
@@ -7298,7 +7298,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Chino</t>
+          <t>zh</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -7307,7 +7307,7 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.8388</v>
+        <v>0.785</v>
       </c>
       <c r="F90" s="2" t="n">
         <v>45332</v>
@@ -7327,7 +7327,7 @@
         <v>8</v>
       </c>
       <c r="K90" t="n">
-        <v>0</v>
+        <v>40000000</v>
       </c>
       <c r="L90" t="n">
         <v>275815986</v>
@@ -7342,7 +7342,7 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -7375,7 +7375,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Inglés</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -7384,7 +7384,7 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>8.0509</v>
+        <v>8.2607</v>
       </c>
       <c r="F91" s="2" t="n">
         <v>44986</v>
@@ -7398,10 +7398,10 @@
         <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>7.1</v>
+        <v>7.115</v>
       </c>
       <c r="J91" t="n">
-        <v>2603</v>
+        <v>2606</v>
       </c>
       <c r="K91" t="n">
         <v>75000000</v>
@@ -7419,7 +7419,7 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>US</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
@@ -7429,7 +7429,7 @@
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
@@ -7452,7 +7452,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Inglés</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -7461,7 +7461,7 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>16.0048</v>
+        <v>13.5061</v>
       </c>
       <c r="F92" s="2" t="n">
         <v>45090</v>
@@ -7475,10 +7475,10 @@
         <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>6.662</v>
+        <v>6.659</v>
       </c>
       <c r="J92" t="n">
-        <v>4466</v>
+        <v>4473</v>
       </c>
       <c r="K92" t="n">
         <v>220000000</v>
@@ -7496,7 +7496,7 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>US</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
@@ -7506,7 +7506,7 @@
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
@@ -7529,7 +7529,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Inglés</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -7538,7 +7538,7 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>15.4765</v>
+        <v>12.4379</v>
       </c>
       <c r="F93" s="2" t="n">
         <v>45175</v>
@@ -7552,10 +7552,10 @@
         <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>6.711</v>
+        <v>6.712</v>
       </c>
       <c r="J93" t="n">
-        <v>2139</v>
+        <v>2144</v>
       </c>
       <c r="K93" t="n">
         <v>38500000</v>
@@ -7573,7 +7573,7 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>US</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -7583,7 +7583,7 @@
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Inglés</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -7615,7 +7615,7 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>24.7039</v>
+        <v>21.4216</v>
       </c>
       <c r="F94" s="2" t="n">
         <v>45469</v>
@@ -7629,10 +7629,10 @@
         <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>6.741</v>
+        <v>6.739</v>
       </c>
       <c r="J94" t="n">
-        <v>2656</v>
+        <v>2676</v>
       </c>
       <c r="K94" t="n">
         <v>67000000</v>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>US</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -7660,7 +7660,7 @@
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
@@ -7683,7 +7683,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Inglés</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -7692,7 +7692,7 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>3.4188</v>
+        <v>4.0925</v>
       </c>
       <c r="F95" s="2" t="n">
         <v>45212</v>
@@ -7706,10 +7706,10 @@
         <v>0</v>
       </c>
       <c r="I95" t="n">
-        <v>8.259</v>
+        <v>8.226000000000001</v>
       </c>
       <c r="J95" t="n">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="K95" t="n">
         <v>15000000</v>
@@ -7727,7 +7727,7 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>US</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
@@ -7737,7 +7737,7 @@
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
@@ -7760,7 +7760,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Inglés</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -7769,7 +7769,7 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>17.6489</v>
+        <v>18.0705</v>
       </c>
       <c r="F96" s="2" t="n">
         <v>44482</v>
@@ -7786,7 +7786,7 @@
         <v>7.595</v>
       </c>
       <c r="J96" t="n">
-        <v>9658</v>
+        <v>9665</v>
       </c>
       <c r="K96" t="n">
         <v>135000000</v>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>US</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
@@ -7814,7 +7814,7 @@
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
@@ -7837,7 +7837,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Japonés</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -7846,7 +7846,7 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>3.9327</v>
+        <v>4.1259</v>
       </c>
       <c r="F97" s="2" t="n">
         <v>44898</v>
@@ -7860,10 +7860,10 @@
         <v>0</v>
       </c>
       <c r="I97" t="n">
-        <v>7.749</v>
+        <v>7.741</v>
       </c>
       <c r="J97" t="n">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="K97" t="n">
         <v>0</v>
@@ -7881,7 +7881,7 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>Japón</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>Japón</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
@@ -7914,7 +7914,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Inglés</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -7923,7 +7923,7 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>12.7589</v>
+        <v>13.6666</v>
       </c>
       <c r="F98" s="2" t="n">
         <v>45243</v>
@@ -7937,10 +7937,10 @@
         <v>0</v>
       </c>
       <c r="I98" t="n">
-        <v>6.3</v>
+        <v>6.319</v>
       </c>
       <c r="J98" t="n">
-        <v>1574</v>
+        <v>1579</v>
       </c>
       <c r="K98" t="n">
         <v>175000000</v>
@@ -7958,7 +7958,7 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>US</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -7968,7 +7968,7 @@
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="R98" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Inglés</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -8000,7 +8000,7 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>23.5052</v>
+        <v>25.4314</v>
       </c>
       <c r="F99" s="2" t="n">
         <v>45412</v>
@@ -8017,7 +8017,7 @@
         <v>7.1</v>
       </c>
       <c r="J99" t="n">
-        <v>1232</v>
+        <v>1236</v>
       </c>
       <c r="K99" t="n">
         <v>60000000</v>
@@ -8035,7 +8035,7 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>Estados Unidos, Reino Unido</t>
+          <t>US, GB</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -8045,7 +8045,7 @@
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>Hong Kong, Reino Unido, Estados Unidos</t>
+          <t>Hong Kong, United Kingdom, United States of America</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
@@ -8068,7 +8068,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Chino</t>
+          <t>zh</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -8077,7 +8077,7 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.2619</v>
+        <v>0.5192</v>
       </c>
       <c r="F100" s="2" t="n">
         <v>44736</v>
@@ -8091,10 +8091,10 @@
         <v>0</v>
       </c>
       <c r="I100" t="n">
-        <v>7.4</v>
+        <v>7.423</v>
       </c>
       <c r="J100" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K100" t="n">
         <v>8800000</v>
@@ -8112,7 +8112,7 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -8145,7 +8145,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Chino</t>
+          <t>zh</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -8154,7 +8154,7 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1.3008</v>
+        <v>1.26</v>
       </c>
       <c r="F101" s="2" t="n">
         <v>45109</v>
@@ -8189,7 +8189,7 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">

--- a/src/static/xlsx/cleaned_data.xlsx
+++ b/src/static/xlsx/cleaned_data.xlsx
@@ -2332,7 +2332,7 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>8.1</v>
+        <v>8.148999999999999</v>
       </c>
       <c r="J25" t="n">
         <v>6494</v>
@@ -4565,7 +4565,7 @@
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>7.722</v>
+        <v>7.7</v>
       </c>
       <c r="J54" t="n">
         <v>6950</v>
@@ -6474,10 +6474,10 @@
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>7.028</v>
+        <v>7.027</v>
       </c>
       <c r="J79" t="n">
-        <v>2970</v>
+        <v>2972</v>
       </c>
       <c r="K79" t="n">
         <v>100000000</v>

--- a/src/static/xlsx/cleaned_data.xlsx
+++ b/src/static/xlsx/cleaned_data.xlsx
@@ -641,7 +641,7 @@
         <v>7.946</v>
       </c>
       <c r="J3" t="n">
-        <v>20654</v>
+        <v>20655</v>
       </c>
       <c r="K3" t="n">
         <v>200000000</v>
@@ -715,10 +715,10 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>7.556</v>
+        <v>7.557</v>
       </c>
       <c r="J4" t="n">
-        <v>5713</v>
+        <v>5718</v>
       </c>
       <c r="K4" t="n">
         <v>200000000</v>
@@ -792,10 +792,10 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>8.180999999999999</v>
+        <v>8.182</v>
       </c>
       <c r="J5" t="n">
-        <v>9705</v>
+        <v>9708</v>
       </c>
       <c r="K5" t="n">
         <v>170000000</v>
@@ -869,7 +869,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>7</v>
+        <v>6.982</v>
       </c>
       <c r="J6" t="n">
         <v>9750</v>
@@ -946,10 +946,10 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>7.6</v>
+        <v>7.624</v>
       </c>
       <c r="J7" t="n">
-        <v>9568</v>
+        <v>9569</v>
       </c>
       <c r="K7" t="n">
         <v>100000000</v>
@@ -1026,7 +1026,7 @@
         <v>7.608</v>
       </c>
       <c r="J8" t="n">
-        <v>7000</v>
+        <v>7003</v>
       </c>
       <c r="K8" t="n">
         <v>200000000</v>
@@ -1100,10 +1100,10 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>7.108</v>
+        <v>7.104</v>
       </c>
       <c r="J9" t="n">
-        <v>2139</v>
+        <v>2141</v>
       </c>
       <c r="K9" t="n">
         <v>150000000</v>
@@ -1254,10 +1254,10 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>7.051</v>
+        <v>7.052</v>
       </c>
       <c r="J11" t="n">
-        <v>2668</v>
+        <v>2670</v>
       </c>
       <c r="K11" t="n">
         <v>100000000</v>
@@ -1331,7 +1331,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>7.264</v>
+        <v>7.3</v>
       </c>
       <c r="J12" t="n">
         <v>9452</v>
@@ -1408,10 +1408,10 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>8.1</v>
+        <v>8.067</v>
       </c>
       <c r="J13" t="n">
-        <v>10057</v>
+        <v>10058</v>
       </c>
       <c r="K13" t="n">
         <v>100000000</v>
@@ -1485,10 +1485,10 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>7.3</v>
+        <v>7.301</v>
       </c>
       <c r="J14" t="n">
-        <v>3699</v>
+        <v>3700</v>
       </c>
       <c r="K14" t="n">
         <v>85000000</v>
@@ -1950,7 +1950,7 @@
         <v>7.655</v>
       </c>
       <c r="J20" t="n">
-        <v>10785</v>
+        <v>10787</v>
       </c>
       <c r="K20" t="n">
         <v>185000000</v>
@@ -2101,10 +2101,10 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>6.933</v>
+        <v>6.934</v>
       </c>
       <c r="J22" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="K22" t="n">
         <v>150000000</v>
@@ -2255,10 +2255,10 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>7.444</v>
+        <v>7.443</v>
       </c>
       <c r="J24" t="n">
-        <v>1862</v>
+        <v>1864</v>
       </c>
       <c r="K24" t="n">
         <v>200000000</v>
@@ -2489,7 +2489,7 @@
         <v>8.345000000000001</v>
       </c>
       <c r="J27" t="n">
-        <v>7450</v>
+        <v>7453</v>
       </c>
       <c r="K27" t="n">
         <v>100000000</v>
@@ -3102,10 +3102,10 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>7.533</v>
+        <v>7.5</v>
       </c>
       <c r="J35" t="n">
-        <v>4116</v>
+        <v>4117</v>
       </c>
       <c r="K35" t="n">
         <v>291000000</v>
@@ -3179,10 +3179,10 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>7.1</v>
+        <v>7.07</v>
       </c>
       <c r="J36" t="n">
-        <v>3021</v>
+        <v>3022</v>
       </c>
       <c r="K36" t="n">
         <v>80000000</v>
@@ -3256,10 +3256,10 @@
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>8.209</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="J37" t="n">
-        <v>4051</v>
+        <v>4052</v>
       </c>
       <c r="K37" t="n">
         <v>15700000</v>
@@ -3333,10 +3333,10 @@
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>6.8</v>
+        <v>6.777</v>
       </c>
       <c r="J38" t="n">
-        <v>10577</v>
+        <v>10578</v>
       </c>
       <c r="K38" t="n">
         <v>110000000</v>
@@ -3487,7 +3487,7 @@
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>7.618</v>
+        <v>7.6</v>
       </c>
       <c r="J40" t="n">
         <v>4743</v>
@@ -3564,10 +3564,10 @@
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>7.8</v>
+        <v>7.764</v>
       </c>
       <c r="J41" t="n">
-        <v>2331</v>
+        <v>2334</v>
       </c>
       <c r="K41" t="n">
         <v>122000000</v>
@@ -3641,10 +3641,10 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>8.217000000000001</v>
+        <v>8.215999999999999</v>
       </c>
       <c r="J42" t="n">
-        <v>8089</v>
+        <v>8090</v>
       </c>
       <c r="K42" t="n">
         <v>90000000</v>
@@ -3795,10 +3795,10 @@
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>6.786</v>
+        <v>6.785</v>
       </c>
       <c r="J44" t="n">
-        <v>3126</v>
+        <v>3128</v>
       </c>
       <c r="K44" t="n">
         <v>120000000</v>
@@ -4026,10 +4026,10 @@
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>7.578</v>
+        <v>7.577</v>
       </c>
       <c r="J47" t="n">
-        <v>10152</v>
+        <v>10153</v>
       </c>
       <c r="K47" t="n">
         <v>200000000</v>
@@ -4334,10 +4334,10 @@
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>6.8</v>
+        <v>6.761</v>
       </c>
       <c r="J51" t="n">
-        <v>3137</v>
+        <v>3139</v>
       </c>
       <c r="K51" t="n">
         <v>310000000</v>
@@ -4411,7 +4411,7 @@
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>7.042</v>
+        <v>7</v>
       </c>
       <c r="J52" t="n">
         <v>2421</v>
@@ -4722,7 +4722,7 @@
         <v>7.524</v>
       </c>
       <c r="J56" t="n">
-        <v>9649</v>
+        <v>9650</v>
       </c>
       <c r="K56" t="n">
         <v>150000000</v>
@@ -4868,7 +4868,7 @@
         <v>7.133</v>
       </c>
       <c r="J58" t="n">
-        <v>8377</v>
+        <v>8378</v>
       </c>
       <c r="K58" t="n">
         <v>90000000</v>
@@ -4942,10 +4942,10 @@
         <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>7.85</v>
+        <v>7.849</v>
       </c>
       <c r="J59" t="n">
-        <v>4482</v>
+        <v>4483</v>
       </c>
       <c r="K59" t="n">
         <v>85000000</v>
@@ -5022,7 +5022,7 @@
         <v>7.782</v>
       </c>
       <c r="J60" t="n">
-        <v>13377</v>
+        <v>13378</v>
       </c>
       <c r="K60" t="n">
         <v>165000000</v>
@@ -5173,10 +5173,10 @@
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>6.9</v>
+        <v>6.915</v>
       </c>
       <c r="J62" t="n">
-        <v>6201</v>
+        <v>6202</v>
       </c>
       <c r="K62" t="n">
         <v>120000000</v>
@@ -5327,10 +5327,10 @@
         <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>7.384</v>
+        <v>7.383</v>
       </c>
       <c r="J64" t="n">
-        <v>2824</v>
+        <v>2826</v>
       </c>
       <c r="K64" t="n">
         <v>100000000</v>
@@ -5858,10 +5858,10 @@
         <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>6.557</v>
+        <v>6.556</v>
       </c>
       <c r="J71" t="n">
-        <v>3607</v>
+        <v>3609</v>
       </c>
       <c r="K71" t="n">
         <v>294700000</v>
@@ -6015,7 +6015,7 @@
         <v>6.855</v>
       </c>
       <c r="J73" t="n">
-        <v>2351</v>
+        <v>2352</v>
       </c>
       <c r="K73" t="n">
         <v>155000000</v>
@@ -6243,10 +6243,10 @@
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>7</v>
+        <v>7.05</v>
       </c>
       <c r="J76" t="n">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="K76" t="n">
         <v>25000000</v>
@@ -6320,10 +6320,10 @@
         <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>7.2</v>
+        <v>7.21</v>
       </c>
       <c r="J77" t="n">
-        <v>3494</v>
+        <v>3495</v>
       </c>
       <c r="K77" t="n">
         <v>80000000</v>
@@ -6628,10 +6628,10 @@
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>8.333</v>
+        <v>8.332000000000001</v>
       </c>
       <c r="J81" t="n">
-        <v>4646</v>
+        <v>4649</v>
       </c>
       <c r="K81" t="n">
         <v>78000000</v>
@@ -6708,7 +6708,7 @@
         <v>7.482</v>
       </c>
       <c r="J82" t="n">
-        <v>9015</v>
+        <v>9016</v>
       </c>
       <c r="K82" t="n">
         <v>110000000</v>
@@ -6782,10 +6782,10 @@
         <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>7.927</v>
+        <v>7.926</v>
       </c>
       <c r="J83" t="n">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="K83" t="n">
         <v>0</v>
@@ -7090,10 +7090,10 @@
         <v>0</v>
       </c>
       <c r="I87" t="n">
-        <v>7.483</v>
+        <v>7.484</v>
       </c>
       <c r="J87" t="n">
-        <v>4279</v>
+        <v>4281</v>
       </c>
       <c r="K87" t="n">
         <v>20000000</v>
@@ -7475,10 +7475,10 @@
         <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>6.659</v>
+        <v>6.66</v>
       </c>
       <c r="J92" t="n">
-        <v>4473</v>
+        <v>4474</v>
       </c>
       <c r="K92" t="n">
         <v>220000000</v>
@@ -7629,10 +7629,10 @@
         <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>6.739</v>
+        <v>6.738</v>
       </c>
       <c r="J94" t="n">
-        <v>2676</v>
+        <v>2678</v>
       </c>
       <c r="K94" t="n">
         <v>67000000</v>
@@ -7706,10 +7706,10 @@
         <v>0</v>
       </c>
       <c r="I95" t="n">
-        <v>8.226000000000001</v>
+        <v>8.227</v>
       </c>
       <c r="J95" t="n">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="K95" t="n">
         <v>15000000</v>
@@ -7940,7 +7940,7 @@
         <v>6.319</v>
       </c>
       <c r="J98" t="n">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="K98" t="n">
         <v>175000000</v>

--- a/src/static/xlsx/cleaned_data.xlsx
+++ b/src/static/xlsx/cleaned_data.xlsx
@@ -872,7 +872,7 @@
         <v>6.982</v>
       </c>
       <c r="J6" t="n">
-        <v>9750</v>
+        <v>9751</v>
       </c>
       <c r="K6" t="n">
         <v>145000000</v>
@@ -2332,10 +2332,10 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>8.148999999999999</v>
+        <v>8.148</v>
       </c>
       <c r="J25" t="n">
-        <v>6494</v>
+        <v>6498</v>
       </c>
       <c r="K25" t="n">
         <v>190000000</v>
@@ -5553,7 +5553,7 @@
         <v>7.082</v>
       </c>
       <c r="J67" t="n">
-        <v>3655</v>
+        <v>3657</v>
       </c>
       <c r="K67" t="n">
         <v>160000000</v>
@@ -6169,7 +6169,7 @@
         <v>7.182</v>
       </c>
       <c r="J75" t="n">
-        <v>10165</v>
+        <v>10166</v>
       </c>
       <c r="K75" t="n">
         <v>205000000</v>
@@ -7786,7 +7786,7 @@
         <v>7.595</v>
       </c>
       <c r="J96" t="n">
-        <v>9665</v>
+        <v>9669</v>
       </c>
       <c r="K96" t="n">
         <v>135000000</v>

--- a/src/static/xlsx/cleaned_data.xlsx
+++ b/src/static/xlsx/cleaned_data.xlsx
@@ -718,7 +718,7 @@
         <v>7.557</v>
       </c>
       <c r="J4" t="n">
-        <v>5718</v>
+        <v>5720</v>
       </c>
       <c r="K4" t="n">
         <v>200000000</v>
@@ -792,10 +792,10 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>8.182</v>
+        <v>8.180999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>9708</v>
+        <v>9709</v>
       </c>
       <c r="K5" t="n">
         <v>170000000</v>
@@ -949,7 +949,7 @@
         <v>7.624</v>
       </c>
       <c r="J7" t="n">
-        <v>9569</v>
+        <v>9570</v>
       </c>
       <c r="K7" t="n">
         <v>100000000</v>
@@ -1026,7 +1026,7 @@
         <v>7.608</v>
       </c>
       <c r="J8" t="n">
-        <v>7003</v>
+        <v>7005</v>
       </c>
       <c r="K8" t="n">
         <v>200000000</v>
@@ -1100,10 +1100,10 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>7.104</v>
+        <v>7.082</v>
       </c>
       <c r="J9" t="n">
-        <v>2141</v>
+        <v>2155</v>
       </c>
       <c r="K9" t="n">
         <v>150000000</v>
@@ -1177,10 +1177,10 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>6.7</v>
+        <v>6.668</v>
       </c>
       <c r="J10" t="n">
-        <v>6303</v>
+        <v>6304</v>
       </c>
       <c r="K10" t="n">
         <v>165000000</v>
@@ -1254,10 +1254,10 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>7.052</v>
+        <v>7.1</v>
       </c>
       <c r="J11" t="n">
-        <v>2670</v>
+        <v>2671</v>
       </c>
       <c r="K11" t="n">
         <v>100000000</v>
@@ -1331,10 +1331,10 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>7.3</v>
+        <v>7.264</v>
       </c>
       <c r="J12" t="n">
-        <v>9452</v>
+        <v>9453</v>
       </c>
       <c r="K12" t="n">
         <v>200000000</v>
@@ -1719,7 +1719,7 @@
         <v>7.948</v>
       </c>
       <c r="J17" t="n">
-        <v>7242</v>
+        <v>7243</v>
       </c>
       <c r="K17" t="n">
         <v>250000000</v>
@@ -2024,10 +2024,10 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>6.42</v>
+        <v>6.421</v>
       </c>
       <c r="J21" t="n">
-        <v>7836</v>
+        <v>7837</v>
       </c>
       <c r="K21" t="n">
         <v>250000000</v>
@@ -2101,10 +2101,10 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>6.934</v>
+        <v>6.931</v>
       </c>
       <c r="J22" t="n">
-        <v>2015</v>
+        <v>2019</v>
       </c>
       <c r="K22" t="n">
         <v>150000000</v>
@@ -2255,10 +2255,10 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>7.443</v>
+        <v>7.415</v>
       </c>
       <c r="J24" t="n">
-        <v>1864</v>
+        <v>1877</v>
       </c>
       <c r="K24" t="n">
         <v>200000000</v>
@@ -2409,10 +2409,10 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>7.049</v>
+        <v>7.048</v>
       </c>
       <c r="J26" t="n">
-        <v>5834</v>
+        <v>5835</v>
       </c>
       <c r="K26" t="n">
         <v>340000000</v>
@@ -2717,10 +2717,10 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>7.086</v>
+        <v>7.085</v>
       </c>
       <c r="J30" t="n">
-        <v>3823</v>
+        <v>3825</v>
       </c>
       <c r="K30" t="n">
         <v>125000000</v>
@@ -2948,10 +2948,10 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>7.1</v>
+        <v>7.098</v>
       </c>
       <c r="J33" t="n">
-        <v>4132</v>
+        <v>4133</v>
       </c>
       <c r="K33" t="n">
         <v>150000000</v>
@@ -3102,10 +3102,10 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>7.5</v>
+        <v>7.534</v>
       </c>
       <c r="J35" t="n">
-        <v>4117</v>
+        <v>4118</v>
       </c>
       <c r="K35" t="n">
         <v>291000000</v>
@@ -3336,7 +3336,7 @@
         <v>6.777</v>
       </c>
       <c r="J38" t="n">
-        <v>10578</v>
+        <v>10579</v>
       </c>
       <c r="K38" t="n">
         <v>110000000</v>
@@ -3564,10 +3564,10 @@
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>7.764</v>
+        <v>7.8</v>
       </c>
       <c r="J41" t="n">
-        <v>2334</v>
+        <v>2335</v>
       </c>
       <c r="K41" t="n">
         <v>122000000</v>
@@ -3644,7 +3644,7 @@
         <v>8.215999999999999</v>
       </c>
       <c r="J42" t="n">
-        <v>8090</v>
+        <v>8091</v>
       </c>
       <c r="K42" t="n">
         <v>90000000</v>
@@ -3795,10 +3795,10 @@
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>6.785</v>
+        <v>6.786</v>
       </c>
       <c r="J44" t="n">
-        <v>3128</v>
+        <v>3132</v>
       </c>
       <c r="K44" t="n">
         <v>120000000</v>
@@ -3875,7 +3875,7 @@
         <v>6.294</v>
       </c>
       <c r="J45" t="n">
-        <v>5212</v>
+        <v>5213</v>
       </c>
       <c r="K45" t="n">
         <v>388369742</v>
@@ -4337,7 +4337,7 @@
         <v>6.761</v>
       </c>
       <c r="J51" t="n">
-        <v>3139</v>
+        <v>3141</v>
       </c>
       <c r="K51" t="n">
         <v>310000000</v>
@@ -4411,10 +4411,10 @@
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>7</v>
+        <v>7.041</v>
       </c>
       <c r="J52" t="n">
-        <v>2421</v>
+        <v>2423</v>
       </c>
       <c r="K52" t="n">
         <v>100000000</v>
@@ -4565,10 +4565,10 @@
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>7.7</v>
+        <v>7.722</v>
       </c>
       <c r="J54" t="n">
-        <v>6950</v>
+        <v>6952</v>
       </c>
       <c r="K54" t="n">
         <v>90000000</v>
@@ -4722,7 +4722,7 @@
         <v>7.524</v>
       </c>
       <c r="J56" t="n">
-        <v>9650</v>
+        <v>9651</v>
       </c>
       <c r="K56" t="n">
         <v>150000000</v>
@@ -5022,7 +5022,7 @@
         <v>7.782</v>
       </c>
       <c r="J60" t="n">
-        <v>13378</v>
+        <v>13380</v>
       </c>
       <c r="K60" t="n">
         <v>165000000</v>
@@ -5253,7 +5253,7 @@
         <v>7.47</v>
       </c>
       <c r="J63" t="n">
-        <v>5431</v>
+        <v>5432</v>
       </c>
       <c r="K63" t="n">
         <v>110000000</v>
@@ -5330,7 +5330,7 @@
         <v>7.383</v>
       </c>
       <c r="J64" t="n">
-        <v>2826</v>
+        <v>2829</v>
       </c>
       <c r="K64" t="n">
         <v>100000000</v>
@@ -5935,7 +5935,7 @@
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>7.209</v>
+        <v>7.2</v>
       </c>
       <c r="J72" t="n">
         <v>10423</v>
@@ -6015,7 +6015,7 @@
         <v>6.855</v>
       </c>
       <c r="J73" t="n">
-        <v>2352</v>
+        <v>2354</v>
       </c>
       <c r="K73" t="n">
         <v>155000000</v>
@@ -6243,10 +6243,10 @@
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>7.05</v>
+        <v>7.049</v>
       </c>
       <c r="J76" t="n">
-        <v>1541</v>
+        <v>1544</v>
       </c>
       <c r="K76" t="n">
         <v>25000000</v>
@@ -6628,10 +6628,10 @@
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>8.332000000000001</v>
+        <v>8.333</v>
       </c>
       <c r="J81" t="n">
-        <v>4649</v>
+        <v>4653</v>
       </c>
       <c r="K81" t="n">
         <v>78000000</v>
@@ -7016,7 +7016,7 @@
         <v>7.473</v>
       </c>
       <c r="J86" t="n">
-        <v>6738</v>
+        <v>6739</v>
       </c>
       <c r="K86" t="n">
         <v>55000000</v>
@@ -7093,7 +7093,7 @@
         <v>7.484</v>
       </c>
       <c r="J87" t="n">
-        <v>4281</v>
+        <v>4282</v>
       </c>
       <c r="K87" t="n">
         <v>20000000</v>
@@ -7167,10 +7167,10 @@
         <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>7.453</v>
+        <v>7.454</v>
       </c>
       <c r="J88" t="n">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="K88" t="n">
         <v>50000000</v>
@@ -7401,7 +7401,7 @@
         <v>7.115</v>
       </c>
       <c r="J91" t="n">
-        <v>2606</v>
+        <v>2607</v>
       </c>
       <c r="K91" t="n">
         <v>75000000</v>
@@ -7552,10 +7552,10 @@
         <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>6.712</v>
+        <v>6.713</v>
       </c>
       <c r="J93" t="n">
-        <v>2144</v>
+        <v>2145</v>
       </c>
       <c r="K93" t="n">
         <v>38500000</v>
@@ -7629,10 +7629,10 @@
         <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>6.738</v>
+        <v>6.739</v>
       </c>
       <c r="J94" t="n">
-        <v>2678</v>
+        <v>2679</v>
       </c>
       <c r="K94" t="n">
         <v>67000000</v>

--- a/src/static/xlsx/cleaned_data.xlsx
+++ b/src/static/xlsx/cleaned_data.xlsx
@@ -1485,10 +1485,10 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>7.301</v>
+        <v>7.302</v>
       </c>
       <c r="J14" t="n">
-        <v>3700</v>
+        <v>3701</v>
       </c>
       <c r="K14" t="n">
         <v>85000000</v>
